--- a/images/2024-07-01-Omnissa-poc/Omnissa-adoption-map.xlsx
+++ b/images/2024-07-01-Omnissa-poc/Omnissa-adoption-map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mbeaugrand/github/blog/images/2024-07-01-Omnissa-poc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CE9559-EF2F-0244-998D-E2F5BC055B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57AC4B74-730D-5642-8B54-55B99C8DA740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23920" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="73">
   <si>
     <t>Testing</t>
   </si>
@@ -61,9 +61,6 @@
     <t>App management</t>
   </si>
   <si>
-    <t>Android mangement</t>
-  </si>
-  <si>
     <t>Android OEM config</t>
   </si>
   <si>
@@ -73,9 +70,6 @@
     <t>Identity integration</t>
   </si>
   <si>
-    <t>Certificate deploymnet</t>
-  </si>
-  <si>
     <t>Content management (MCM)</t>
   </si>
   <si>
@@ -242,6 +236,9 @@
   </si>
   <si>
     <t>Risk based signals</t>
+  </si>
+  <si>
+    <t>Android management</t>
   </si>
 </sst>
 </file>
@@ -470,9 +467,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -498,6 +492,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -875,45 +872,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="97" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27"/>
-      <c r="B1" s="29"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="30"/>
+      <c r="A1" s="26"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="29"/>
     </row>
     <row r="2" spans="1:15" ht="35" x14ac:dyDescent="0.2">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="26" t="s">
-        <v>63</v>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="25" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="33" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="14"/>
@@ -921,48 +918,48 @@
         <v>11</v>
       </c>
       <c r="E4" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="I4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="8" t="s">
-        <v>16</v>
-      </c>
       <c r="M4" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="23"/>
+      <c r="A5" s="33"/>
       <c r="B5" s="14"/>
     </row>
     <row r="6" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A6" s="23"/>
+      <c r="A6" s="33"/>
       <c r="B6" s="14"/>
       <c r="C6" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" s="9" t="s">
+      <c r="M6" s="10" t="s">
         <v>20</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" s="10" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="20" thickBot="1" x14ac:dyDescent="0.3">
@@ -983,7 +980,7 @@
       <c r="O7" s="4"/>
     </row>
     <row r="8" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A8" s="31"/>
+      <c r="A8" s="30"/>
       <c r="B8" s="16"/>
       <c r="C8" s="5"/>
       <c r="D8" s="6"/>
@@ -1000,31 +997,31 @@
       <c r="O8" s="5"/>
     </row>
     <row r="9" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A9" s="32" t="s">
-        <v>56</v>
+      <c r="A9" s="31" t="s">
+        <v>54</v>
       </c>
       <c r="B9" s="14"/>
       <c r="C9" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="I9" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="K9" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="M9" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="K9" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>62</v>
-      </c>
     </row>
     <row r="10" spans="1:15" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="33"/>
+      <c r="A10" s="32"/>
       <c r="B10" s="17"/>
       <c r="C10" s="4"/>
       <c r="D10" s="3"/>
@@ -1045,70 +1042,70 @@
       <c r="B11" s="18"/>
     </row>
     <row r="12" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A12" s="23" t="s">
-        <v>23</v>
+      <c r="A12" s="33" t="s">
+        <v>21</v>
       </c>
       <c r="B12" s="14"/>
       <c r="C12" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="I12" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>27</v>
-      </c>
       <c r="K12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="M12" s="8" t="s">
-        <v>16</v>
-      </c>
       <c r="O12" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="23"/>
+      <c r="A13" s="33"/>
       <c r="B13" s="14"/>
     </row>
     <row r="14" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A14" s="23"/>
+      <c r="A14" s="33"/>
       <c r="B14" s="14"/>
       <c r="C14" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>12</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I14" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="M14" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K14" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="M14" s="9" t="s">
-        <v>22</v>
-      </c>
       <c r="O14" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="23"/>
+      <c r="A15" s="33"/>
       <c r="B15" s="14"/>
     </row>
     <row r="16" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A16" s="23"/>
+      <c r="A16" s="33"/>
       <c r="B16" s="14"/>
       <c r="C16" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E16" s="20"/>
       <c r="G16" s="20"/>
@@ -1135,7 +1132,7 @@
       <c r="O17" s="4"/>
     </row>
     <row r="18" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A18" s="31"/>
+      <c r="A18" s="30"/>
       <c r="B18" s="16"/>
       <c r="C18" s="5"/>
       <c r="D18" s="6"/>
@@ -1152,34 +1149,34 @@
       <c r="O18" s="5"/>
     </row>
     <row r="19" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A19" s="32" t="s">
-        <v>31</v>
+      <c r="A19" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="G19" s="19" t="s">
         <v>26</v>
-      </c>
-      <c r="G19" s="19" t="s">
-        <v>28</v>
       </c>
       <c r="I19" s="19" t="s">
         <v>12</v>
       </c>
       <c r="K19" s="19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M19" s="19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O19" s="19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="33"/>
+      <c r="A20" s="32"/>
       <c r="B20" s="17"/>
       <c r="C20" s="4"/>
       <c r="D20" s="3"/>
@@ -1200,47 +1197,47 @@
       <c r="B21" s="18"/>
     </row>
     <row r="22" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A22" s="23" t="s">
-        <v>34</v>
+      <c r="A22" s="33" t="s">
+        <v>32</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>1</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K22" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="O22" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="M22" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="O22" s="8" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="23" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="23"/>
+      <c r="A23" s="33"/>
       <c r="B23" s="14"/>
     </row>
     <row r="24" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A24" s="23"/>
+      <c r="A24" s="33"/>
       <c r="B24" s="14"/>
       <c r="C24" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="20" thickBot="1" x14ac:dyDescent="0.25">
@@ -1265,44 +1262,44 @@
       <c r="B26" s="18"/>
     </row>
     <row r="27" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A27" s="23" t="s">
-        <v>42</v>
+      <c r="A27" s="33" t="s">
+        <v>40</v>
       </c>
       <c r="B27" s="14"/>
       <c r="C27" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I27" s="11" t="s">
         <v>3</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O27" s="11" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="23"/>
+      <c r="A28" s="33"/>
       <c r="B28" s="14"/>
     </row>
     <row r="29" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A29" s="23"/>
+      <c r="A29" s="33"/>
       <c r="B29" s="14"/>
       <c r="C29" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="20" thickBot="1" x14ac:dyDescent="0.25">
@@ -1327,38 +1324,38 @@
       <c r="B31" s="18"/>
     </row>
     <row r="32" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A32" s="23" t="s">
-        <v>49</v>
+      <c r="A32" s="33" t="s">
+        <v>47</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G32" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E32" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>52</v>
-      </c>
       <c r="I32" s="9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K32" s="8" t="s">
         <v>5</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O32" s="9" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="23"/>
+      <c r="A33" s="33"/>
       <c r="B33" s="14"/>
     </row>
     <row r="34" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A34" s="23"/>
+      <c r="A34" s="33"/>
       <c r="B34" s="14"/>
       <c r="C34" s="9" t="s">
         <v>7</v>
@@ -1370,13 +1367,13 @@
         <v>8</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M34" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
@@ -1398,19 +1395,19 @@
     </row>
     <row r="38" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="G38" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K38" s="10" t="s">
         <v>0</v>
       </c>
       <c r="M38" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O38" s="19" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/images/2024-07-01-Omnissa-poc/Omnissa-adoption-map.xlsx
+++ b/images/2024-07-01-Omnissa-poc/Omnissa-adoption-map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mbeaugrand/github/blog/images/2024-07-01-Omnissa-poc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57AC4B74-730D-5642-8B54-55B99C8DA740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A0265E-BD16-8C44-9EB5-E05EAD19FC64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23920" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="76">
   <si>
     <t>Testing</t>
   </si>
@@ -239,13 +239,22 @@
   </si>
   <si>
     <t>Android management</t>
+  </si>
+  <si>
+    <t>Secure Access Suite</t>
+  </si>
+  <si>
+    <t>Launcher</t>
+  </si>
+  <si>
+    <t>Pass</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -303,8 +312,23 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -338,30 +362,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -402,6 +420,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -409,20 +445,12 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -445,13 +473,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -467,33 +488,56 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -527,7 +571,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1562100</xdr:colOff>
+      <xdr:colOff>1752600</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>1221257</xdr:rowOff>
     </xdr:to>
@@ -850,10 +894,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA5F0923-2FA0-B442-B432-F0C48886CD46}">
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.83203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="1.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="25.83203125" style="2" customWidth="1"/>
     <col min="4" max="4" width="1.83203125" style="1" customWidth="1"/>
@@ -872,551 +916,597 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="97" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26"/>
-      <c r="B1" s="28"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="29"/>
+      <c r="A1" s="16"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="19"/>
     </row>
     <row r="2" spans="1:15" ht="35" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="25" t="s">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="22" t="s">
         <v>61</v>
       </c>
     </row>
+    <row r="3" spans="1:15" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="23"/>
+    </row>
     <row r="4" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="10"/>
+      <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="M4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="O4" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="33"/>
-      <c r="B5" s="14"/>
+      <c r="A5" s="24"/>
+      <c r="B5" s="10"/>
     </row>
     <row r="6" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A6" s="33"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="8" t="s">
+      <c r="A6" s="24"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="M6" s="10" t="s">
+      <c r="M6" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="4"/>
-    </row>
-    <row r="8" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A8" s="30"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="5"/>
+    <row r="7" spans="1:15" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="33"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="37"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="37"/>
+    </row>
+    <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="29"/>
     </row>
     <row r="9" spans="1:15" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="11" t="s">
+      <c r="B9" s="10"/>
+      <c r="C9" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M9" s="7" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="32"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="4"/>
-    </row>
-    <row r="11" spans="1:15" ht="19" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-    </row>
-    <row r="12" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A12" s="33" t="s">
+      <c r="O9" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="31"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="29"/>
+    </row>
+    <row r="11" spans="1:15" ht="19" x14ac:dyDescent="0.2">
+      <c r="A11" s="31"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="30"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="29"/>
+    </row>
+    <row r="12" spans="1:15" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="33"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="37"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="37"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="37"/>
+    </row>
+    <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="26"/>
+      <c r="B13" s="11"/>
+    </row>
+    <row r="14" spans="1:15" ht="19" x14ac:dyDescent="0.2">
+      <c r="A14" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="8" t="s">
+      <c r="B14" s="10"/>
+      <c r="C14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E14" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I14" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K14" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="M14" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="O12" s="8" t="s">
+      <c r="O14" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="33"/>
-      <c r="B13" s="14"/>
-    </row>
-    <row r="14" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A14" s="33"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="8" t="s">
+    <row r="15" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="24"/>
+      <c r="B15" s="10"/>
+    </row>
+    <row r="16" spans="1:15" ht="19" x14ac:dyDescent="0.2">
+      <c r="A16" s="24"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G16" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="9" t="s">
+      <c r="K16" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="M14" s="9" t="s">
+      <c r="M16" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="O14" s="10" t="s">
+      <c r="O16" s="6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="33"/>
-      <c r="B15" s="14"/>
-    </row>
-    <row r="16" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A16" s="33"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="9" t="s">
+    <row r="17" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="24"/>
+      <c r="B17" s="10"/>
+    </row>
+    <row r="18" spans="1:15" ht="19" x14ac:dyDescent="0.2">
+      <c r="A18" s="24"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="I16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="M16" s="21"/>
-      <c r="O16" s="22"/>
-    </row>
-    <row r="17" spans="1:15" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="4"/>
-    </row>
-    <row r="18" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A18" s="30"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="5"/>
-    </row>
-    <row r="19" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A19" s="31" t="s">
+      <c r="E18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="I18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="O18" s="15"/>
+    </row>
+    <row r="19" spans="1:15" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="33"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="37"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="37"/>
+    </row>
+    <row r="20" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="38"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="36"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="29"/>
+    </row>
+    <row r="21" spans="1:15" ht="19" x14ac:dyDescent="0.2">
+      <c r="A21" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="19" t="s">
+      <c r="B21" s="10"/>
+      <c r="C21" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E21" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G19" s="19" t="s">
+      <c r="G21" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="I19" s="19" t="s">
+      <c r="I21" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="K19" s="19" t="s">
+      <c r="K21" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="M19" s="19" t="s">
+      <c r="M21" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="O19" s="19" t="s">
+      <c r="O21" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="32"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="4"/>
-    </row>
-    <row r="21" spans="1:15" ht="19" x14ac:dyDescent="0.25">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-    </row>
-    <row r="22" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A22" s="33" t="s">
+    <row r="22" spans="1:15" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="33"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="37"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="37"/>
+    </row>
+    <row r="23" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="26"/>
+      <c r="B23" s="11"/>
+    </row>
+    <row r="24" spans="1:15" ht="19" x14ac:dyDescent="0.2">
+      <c r="A24" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="8" t="s">
+      <c r="B24" s="10"/>
+      <c r="C24" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E24" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G24" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="I22" s="9" t="s">
+      <c r="I24" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="K22" s="8" t="s">
+      <c r="K24" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="M22" s="8" t="s">
+      <c r="M24" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="O22" s="8" t="s">
+      <c r="O24" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="33"/>
-      <c r="B23" s="14"/>
-    </row>
-    <row r="24" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A24" s="33"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="9" t="s">
+    <row r="25" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="24"/>
+      <c r="B25" s="10"/>
+    </row>
+    <row r="26" spans="1:15" ht="19" x14ac:dyDescent="0.2">
+      <c r="A26" s="24"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E26" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G24" s="19" t="s">
+      <c r="G26" s="12" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="4"/>
-    </row>
-    <row r="26" spans="1:15" ht="19" x14ac:dyDescent="0.25">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-    </row>
-    <row r="27" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A27" s="33" t="s">
+      <c r="I26" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="33"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="37"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="37"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="37"/>
+      <c r="N27" s="35"/>
+      <c r="O27" s="37"/>
+    </row>
+    <row r="28" spans="1:15" ht="19" x14ac:dyDescent="0.25">
+      <c r="A28" s="26"/>
+      <c r="B28" s="11"/>
+    </row>
+    <row r="29" spans="1:15" ht="19" x14ac:dyDescent="0.2">
+      <c r="A29" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="12" t="s">
+      <c r="B29" s="10"/>
+      <c r="C29" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E29" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="G27" s="12" t="s">
+      <c r="G29" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="I29" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="K27" s="11" t="s">
+      <c r="K29" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="M27" s="13" t="s">
+      <c r="M29" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="O27" s="11" t="s">
+      <c r="O29" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="33"/>
-      <c r="B28" s="14"/>
-    </row>
-    <row r="29" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A29" s="33"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="11" t="s">
+    <row r="30" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="24"/>
+      <c r="B30" s="10"/>
+    </row>
+    <row r="31" spans="1:15" ht="19" x14ac:dyDescent="0.2">
+      <c r="A31" s="24"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E31" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="3"/>
-      <c r="O30" s="4"/>
-    </row>
-    <row r="31" spans="1:15" ht="19" x14ac:dyDescent="0.25">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-    </row>
-    <row r="32" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A32" s="33" t="s">
+    <row r="32" spans="1:15" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="33"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="37"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="37"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="37"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="37"/>
+      <c r="N32" s="35"/>
+      <c r="O32" s="37"/>
+    </row>
+    <row r="33" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="26"/>
+      <c r="B33" s="11"/>
+    </row>
+    <row r="34" spans="1:15" ht="19" x14ac:dyDescent="0.2">
+      <c r="A34" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="8" t="s">
+      <c r="B34" s="10"/>
+      <c r="C34" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="E34" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="G34" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="I32" s="9" t="s">
+      <c r="I34" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K32" s="8" t="s">
+      <c r="K34" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="M32" s="8" t="s">
+      <c r="M34" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="O32" s="9" t="s">
+      <c r="O34" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="33"/>
-      <c r="B33" s="14"/>
-    </row>
-    <row r="34" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A34" s="33"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="9" t="s">
+    <row r="35" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="24"/>
+      <c r="B35" s="10"/>
+    </row>
+    <row r="36" spans="1:15" ht="19" x14ac:dyDescent="0.2">
+      <c r="A36" s="24"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="E36" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="G36" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I34" s="9" t="s">
+      <c r="I36" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="K34" s="9" t="s">
+      <c r="K36" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="M34" s="9" t="s">
+      <c r="M36" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="3"/>
-      <c r="O35" s="4"/>
-    </row>
-    <row r="38" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="G38" s="7" t="s">
+    <row r="37" spans="1:15" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="33"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="37"/>
+      <c r="J37" s="35"/>
+      <c r="K37" s="37"/>
+      <c r="L37" s="35"/>
+      <c r="M37" s="37"/>
+      <c r="N37" s="35"/>
+      <c r="O37" s="37"/>
+    </row>
+    <row r="40" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="G40" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="I38" s="8" t="s">
+      <c r="I40" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="K38" s="10" t="s">
+      <c r="K40" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="M38" s="9" t="s">
+      <c r="M40" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="O38" s="19" t="s">
+      <c r="O40" s="12" t="s">
         <v>62</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A12:A16"/>
+  <mergeCells count="6">
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="A14:A18"/>
     <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A9:A11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/images/2024-07-01-Omnissa-poc/Omnissa-adoption-map.xlsx
+++ b/images/2024-07-01-Omnissa-poc/Omnissa-adoption-map.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mbeaugrand/github/blog/images/2024-07-01-Omnissa-poc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A0265E-BD16-8C44-9EB5-E05EAD19FC64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F60C2D4-17EA-0F48-B4B6-3640803DFF2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23920" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14480" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Workspace ONE" sheetId="2" r:id="rId1"/>
+    <sheet name="Company profile" sheetId="3" r:id="rId1"/>
+    <sheet name="Adoption - WS1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="167">
   <si>
     <t>Testing</t>
   </si>
@@ -248,13 +249,286 @@
   </si>
   <si>
     <t>Pass</t>
+  </si>
+  <si>
+    <t>Company profile</t>
+  </si>
+  <si>
+    <t>Vertical</t>
+  </si>
+  <si>
+    <t># Employees</t>
+  </si>
+  <si>
+    <t># Contractors</t>
+  </si>
+  <si>
+    <t>Organisation</t>
+  </si>
+  <si>
+    <t>Fixed vs Roaming %</t>
+  </si>
+  <si>
+    <t>Headcount growth %</t>
+  </si>
+  <si>
+    <t>Attrition p/y %</t>
+  </si>
+  <si>
+    <t># Business units</t>
+  </si>
+  <si>
+    <t># Office locations</t>
+  </si>
+  <si>
+    <t># Geographies</t>
+  </si>
+  <si>
+    <t>Preferred partner</t>
+  </si>
+  <si>
+    <t>Preferred distributor</t>
+  </si>
+  <si>
+    <t>MSP</t>
+  </si>
+  <si>
+    <t>Core values</t>
+  </si>
+  <si>
+    <t>Org's revenue streams</t>
+  </si>
+  <si>
+    <t>Infrastructure</t>
+  </si>
+  <si>
+    <t>Primary DC site</t>
+  </si>
+  <si>
+    <t>Secondary DC site</t>
+  </si>
+  <si>
+    <t>Server OEM</t>
+  </si>
+  <si>
+    <t>Hypervisor</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>Cloud provider 1</t>
+  </si>
+  <si>
+    <t>Cloud provider 2</t>
+  </si>
+  <si>
+    <t>Network</t>
+  </si>
+  <si>
+    <t>Network OEM</t>
+  </si>
+  <si>
+    <t>Network virtualisation</t>
+  </si>
+  <si>
+    <t>Software defined network</t>
+  </si>
+  <si>
+    <t>Load balancer</t>
+  </si>
+  <si>
+    <t>GSLB</t>
+  </si>
+  <si>
+    <t>VPN</t>
+  </si>
+  <si>
+    <t>SASE</t>
+  </si>
+  <si>
+    <t>Identity</t>
+  </si>
+  <si>
+    <t>Directory</t>
+  </si>
+  <si>
+    <t>Identity provider</t>
+  </si>
+  <si>
+    <t>MFA solution</t>
+  </si>
+  <si>
+    <t>SSO</t>
+  </si>
+  <si>
+    <t>Conditional access</t>
+  </si>
+  <si>
+    <t>Compliance check</t>
+  </si>
+  <si>
+    <t>Azure AD license</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>EDR/ZDR</t>
+  </si>
+  <si>
+    <t>MTD</t>
+  </si>
+  <si>
+    <t>Firewall</t>
+  </si>
+  <si>
+    <t>Proxy</t>
+  </si>
+  <si>
+    <t>ZTNA</t>
+  </si>
+  <si>
+    <t>CASB</t>
+  </si>
+  <si>
+    <t>SIEM</t>
+  </si>
+  <si>
+    <t>Device management</t>
+  </si>
+  <si>
+    <t>VDI</t>
+  </si>
+  <si>
+    <t>Services</t>
+  </si>
+  <si>
+    <t>Applications</t>
+  </si>
+  <si>
+    <t>Mobile management</t>
+  </si>
+  <si>
+    <t>Rugged management</t>
+  </si>
+  <si>
+    <t>IoT management</t>
+  </si>
+  <si>
+    <t>Patch management</t>
+  </si>
+  <si>
+    <t>VDI provider</t>
+  </si>
+  <si>
+    <t># Virtual desktops</t>
+  </si>
+  <si>
+    <t># Virtual apps</t>
+  </si>
+  <si>
+    <t>OS (client vs server)</t>
+  </si>
+  <si>
+    <t>Presistent vs non persistent</t>
+  </si>
+  <si>
+    <t>User profiles management</t>
+  </si>
+  <si>
+    <t>Productivity tool</t>
+  </si>
+  <si>
+    <t>MS/G-Suite license</t>
+  </si>
+  <si>
+    <t>ITSM tool</t>
+  </si>
+  <si>
+    <t>HR system</t>
+  </si>
+  <si>
+    <t>End user self-service</t>
+  </si>
+  <si>
+    <t>Experience management</t>
+  </si>
+  <si>
+    <t>Experience surveys</t>
+  </si>
+  <si>
+    <t>Desktop apps</t>
+  </si>
+  <si>
+    <t>SaaS apps</t>
+  </si>
+  <si>
+    <t>Mobile apps</t>
+  </si>
+  <si>
+    <t>Endpoints</t>
+  </si>
+  <si>
+    <t># Windows</t>
+  </si>
+  <si>
+    <t>Windows OEM</t>
+  </si>
+  <si>
+    <t># macOS</t>
+  </si>
+  <si>
+    <t>macOS models</t>
+  </si>
+  <si>
+    <t># Chromebook</t>
+  </si>
+  <si>
+    <t>Chromebook OEM</t>
+  </si>
+  <si>
+    <t># iOS</t>
+  </si>
+  <si>
+    <t>iOS models</t>
+  </si>
+  <si>
+    <t># Android</t>
+  </si>
+  <si>
+    <t>Android OEM</t>
+  </si>
+  <si>
+    <t># Rugged mobile</t>
+  </si>
+  <si>
+    <t>Rugged OEM</t>
+  </si>
+  <si>
+    <t># Thin clients</t>
+  </si>
+  <si>
+    <t>Thin client OEM</t>
+  </si>
+  <si>
+    <t># Wireless printers</t>
+  </si>
+  <si>
+    <t>Printer OEM</t>
+  </si>
+  <si>
+    <t># AR headsets</t>
+  </si>
+  <si>
+    <t>AR headsets OEM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -327,8 +601,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -374,8 +667,32 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -438,6 +755,138 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -445,7 +894,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -507,26 +956,10 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
@@ -538,6 +971,159 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -561,6 +1147,55 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1752600</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1221257</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BED5B29E-D7F2-B54C-ACEF-508FFA783F1F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="3657600" cy="1221257"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -893,6 +1528,1334 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D45A99E4-0542-7640-BE42-3DA4CCD6A563}">
+  <dimension ref="A1:O176"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="1.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="1.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="25.83203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="1.83203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="25.83203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="1.83203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25.83203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="1.83203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="25.83203125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="1.83203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="25.83203125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="1.83203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="25.83203125" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="16"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="19"/>
+    </row>
+    <row r="2" spans="1:15" ht="35" x14ac:dyDescent="0.2">
+      <c r="A2" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="22"/>
+    </row>
+    <row r="3" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="43"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+    </row>
+    <row r="4" spans="1:15" s="44" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="39"/>
+    </row>
+    <row r="5" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="35"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="35"/>
+    </row>
+    <row r="6" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="35"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="46" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" s="35"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="J6" s="35"/>
+      <c r="K6" s="58"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="59"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="60"/>
+    </row>
+    <row r="7" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="35"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="61"/>
+    </row>
+    <row r="8" spans="1:15" s="44" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="35"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="F8" s="35"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="56"/>
+      <c r="L8" s="36"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="61"/>
+    </row>
+    <row r="9" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="35"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="56"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="61"/>
+    </row>
+    <row r="10" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="35"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="F10" s="35"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="62"/>
+      <c r="L10" s="63"/>
+      <c r="M10" s="63"/>
+      <c r="N10" s="63"/>
+      <c r="O10" s="64"/>
+    </row>
+    <row r="11" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="35"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="35"/>
+      <c r="O11" s="35"/>
+    </row>
+    <row r="12" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="35"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="F12" s="35"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="J12" s="35"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="66"/>
+      <c r="M12" s="66"/>
+      <c r="N12" s="66"/>
+      <c r="O12" s="67"/>
+    </row>
+    <row r="13" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="35"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="57"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="37"/>
+      <c r="N13" s="37"/>
+      <c r="O13" s="68"/>
+    </row>
+    <row r="14" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" s="35"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="50"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="57"/>
+      <c r="L14" s="37"/>
+      <c r="M14" s="37"/>
+      <c r="N14" s="37"/>
+      <c r="O14" s="68"/>
+    </row>
+    <row r="15" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="35"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="57"/>
+      <c r="L15" s="37"/>
+      <c r="M15" s="37"/>
+      <c r="N15" s="37"/>
+      <c r="O15" s="68"/>
+    </row>
+    <row r="16" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="35"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="F16" s="35"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="69"/>
+      <c r="L16" s="70"/>
+      <c r="M16" s="70"/>
+      <c r="N16" s="70"/>
+      <c r="O16" s="71"/>
+    </row>
+    <row r="17" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="35"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="35"/>
+    </row>
+    <row r="18" spans="1:15" s="44" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="55" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="55"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" s="55"/>
+      <c r="G18" s="55"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="J18" s="55"/>
+      <c r="K18" s="55"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="55" t="s">
+        <v>116</v>
+      </c>
+      <c r="N18" s="55"/>
+      <c r="O18" s="55"/>
+    </row>
+    <row r="19" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="35"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="35"/>
+    </row>
+    <row r="20" spans="1:15" s="44" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="52" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="35"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="52" t="s">
+        <v>101</v>
+      </c>
+      <c r="F20" s="35"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="J20" s="35"/>
+      <c r="K20" s="49"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="N20" s="35"/>
+      <c r="O20" s="49"/>
+    </row>
+    <row r="21" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="35"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="35"/>
+    </row>
+    <row r="22" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="52" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="35"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="F22" s="35"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="J22" s="35"/>
+      <c r="K22" s="49"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="52" t="s">
+        <v>118</v>
+      </c>
+      <c r="N22" s="35"/>
+      <c r="O22" s="49"/>
+    </row>
+    <row r="23" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="35"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="35"/>
+    </row>
+    <row r="24" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" s="35"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="F24" s="35"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="J24" s="35"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="54" t="s">
+        <v>119</v>
+      </c>
+      <c r="N24" s="35"/>
+      <c r="O24" s="45"/>
+    </row>
+    <row r="25" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="35"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="35"/>
+    </row>
+    <row r="26" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="35"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26" s="35"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="J26" s="35"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="52" t="s">
+        <v>120</v>
+      </c>
+      <c r="N26" s="35"/>
+      <c r="O26" s="49"/>
+    </row>
+    <row r="27" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="35"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="35"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="35"/>
+      <c r="N27" s="35"/>
+      <c r="O27" s="35"/>
+    </row>
+    <row r="28" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" s="35"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="F28" s="35"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="J28" s="35"/>
+      <c r="K28" s="49"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="52" t="s">
+        <v>121</v>
+      </c>
+      <c r="N28" s="35"/>
+      <c r="O28" s="49"/>
+    </row>
+    <row r="29" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="35"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="35"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
+      <c r="O29" s="35"/>
+    </row>
+    <row r="30" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="52" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" s="35"/>
+      <c r="C30" s="49"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="F30" s="35"/>
+      <c r="G30" s="49"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="J30" s="35"/>
+      <c r="K30" s="49"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="N30" s="35"/>
+      <c r="O30" s="49"/>
+    </row>
+    <row r="31" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="35"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+    </row>
+    <row r="32" spans="1:15" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="B32" s="35"/>
+      <c r="C32" s="49"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="F32" s="35"/>
+      <c r="G32" s="49"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="52" t="s">
+        <v>115</v>
+      </c>
+      <c r="J32" s="35"/>
+      <c r="K32" s="49"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="52" t="s">
+        <v>123</v>
+      </c>
+      <c r="N32" s="35"/>
+      <c r="O32" s="49"/>
+    </row>
+    <row r="33" spans="1:15" s="44" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="35"/>
+      <c r="B33" s="35"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="35"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="35"/>
+      <c r="I33" s="35"/>
+      <c r="J33" s="35"/>
+      <c r="K33" s="35"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
+      <c r="O33" s="35"/>
+    </row>
+    <row r="34" spans="1:15" s="44" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="72" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" s="72"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="72" t="s">
+        <v>125</v>
+      </c>
+      <c r="F34" s="72"/>
+      <c r="G34" s="72"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J34" s="72"/>
+      <c r="K34" s="72"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="72" t="s">
+        <v>127</v>
+      </c>
+      <c r="N34" s="72"/>
+      <c r="O34" s="72"/>
+    </row>
+    <row r="35" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="35"/>
+      <c r="B35" s="35"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="35"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="35"/>
+      <c r="N35" s="35"/>
+      <c r="O35" s="35"/>
+    </row>
+    <row r="36" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="77" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" s="35"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="78" t="s">
+        <v>132</v>
+      </c>
+      <c r="F36" s="35"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="78" t="s">
+        <v>138</v>
+      </c>
+      <c r="J36" s="35"/>
+      <c r="K36" s="47"/>
+      <c r="L36" s="35"/>
+      <c r="M36" s="73" t="s">
+        <v>145</v>
+      </c>
+      <c r="N36" s="35"/>
+      <c r="O36" s="40"/>
+    </row>
+    <row r="37" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="35"/>
+      <c r="B37" s="35"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="35"/>
+      <c r="J37" s="35"/>
+      <c r="K37" s="35"/>
+      <c r="L37" s="35"/>
+      <c r="M37" s="73"/>
+      <c r="N37" s="35"/>
+      <c r="O37" s="41"/>
+    </row>
+    <row r="38" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="77" t="s">
+        <v>23</v>
+      </c>
+      <c r="B38" s="35"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="35"/>
+      <c r="E38" s="77" t="s">
+        <v>133</v>
+      </c>
+      <c r="F38" s="35"/>
+      <c r="G38" s="49"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="77" t="s">
+        <v>139</v>
+      </c>
+      <c r="J38" s="35"/>
+      <c r="K38" s="49"/>
+      <c r="L38" s="35"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="35"/>
+      <c r="O38" s="42"/>
+    </row>
+    <row r="39" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="35"/>
+      <c r="B39" s="35"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="35"/>
+      <c r="G39" s="35"/>
+      <c r="H39" s="35"/>
+      <c r="I39" s="35"/>
+      <c r="J39" s="35"/>
+      <c r="K39" s="35"/>
+      <c r="L39" s="35"/>
+      <c r="M39" s="35"/>
+      <c r="N39" s="35"/>
+      <c r="O39" s="35"/>
+    </row>
+    <row r="40" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="77" t="s">
+        <v>128</v>
+      </c>
+      <c r="B40" s="35"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="77" t="s">
+        <v>134</v>
+      </c>
+      <c r="F40" s="35"/>
+      <c r="G40" s="49"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="76" t="s">
+        <v>140</v>
+      </c>
+      <c r="J40" s="35"/>
+      <c r="K40" s="79"/>
+      <c r="L40" s="35"/>
+      <c r="M40" s="73" t="s">
+        <v>146</v>
+      </c>
+      <c r="N40" s="35"/>
+      <c r="O40" s="40"/>
+    </row>
+    <row r="41" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="35"/>
+      <c r="B41" s="35"/>
+      <c r="C41" s="35"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="35"/>
+      <c r="H41" s="35"/>
+      <c r="I41" s="35"/>
+      <c r="J41" s="35"/>
+      <c r="K41" s="35"/>
+      <c r="L41" s="35"/>
+      <c r="M41" s="73"/>
+      <c r="N41" s="35"/>
+      <c r="O41" s="41"/>
+    </row>
+    <row r="42" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="75" t="s">
+        <v>129</v>
+      </c>
+      <c r="B42" s="43"/>
+      <c r="C42" s="49"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="75" t="s">
+        <v>135</v>
+      </c>
+      <c r="F42" s="43"/>
+      <c r="G42" s="49"/>
+      <c r="H42" s="43"/>
+      <c r="I42" s="75" t="s">
+        <v>141</v>
+      </c>
+      <c r="J42" s="43"/>
+      <c r="K42" s="49"/>
+      <c r="L42" s="43"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="43"/>
+      <c r="O42" s="42"/>
+    </row>
+    <row r="43" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="35"/>
+      <c r="B43" s="35"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="35"/>
+      <c r="H43" s="35"/>
+      <c r="I43" s="35"/>
+      <c r="J43" s="35"/>
+      <c r="K43" s="35"/>
+      <c r="L43" s="35"/>
+      <c r="M43" s="35"/>
+      <c r="N43" s="35"/>
+      <c r="O43" s="35"/>
+    </row>
+    <row r="44" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="B44" s="43"/>
+      <c r="C44" s="49"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="75" t="s">
+        <v>136</v>
+      </c>
+      <c r="F44" s="43"/>
+      <c r="G44" s="49"/>
+      <c r="H44" s="43"/>
+      <c r="I44" s="75" t="s">
+        <v>142</v>
+      </c>
+      <c r="J44" s="43"/>
+      <c r="K44" s="49"/>
+      <c r="L44" s="43"/>
+      <c r="M44" s="74" t="s">
+        <v>147</v>
+      </c>
+      <c r="N44" s="43"/>
+      <c r="O44" s="40"/>
+    </row>
+    <row r="45" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="35"/>
+      <c r="B45" s="35"/>
+      <c r="C45" s="35"/>
+      <c r="D45" s="35"/>
+      <c r="E45" s="35"/>
+      <c r="F45" s="35"/>
+      <c r="G45" s="35"/>
+      <c r="H45" s="35"/>
+      <c r="I45" s="35"/>
+      <c r="J45" s="35"/>
+      <c r="K45" s="35"/>
+      <c r="L45" s="35"/>
+      <c r="M45" s="74"/>
+      <c r="N45" s="35"/>
+      <c r="O45" s="41"/>
+    </row>
+    <row r="46" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="B46" s="43"/>
+      <c r="C46" s="49"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="75" t="s">
+        <v>137</v>
+      </c>
+      <c r="F46" s="43"/>
+      <c r="G46" s="49"/>
+      <c r="H46" s="43"/>
+      <c r="I46" s="75" t="s">
+        <v>143</v>
+      </c>
+      <c r="J46" s="43"/>
+      <c r="K46" s="49"/>
+      <c r="L46" s="43"/>
+      <c r="M46" s="74"/>
+      <c r="N46" s="43"/>
+      <c r="O46" s="42"/>
+    </row>
+    <row r="47" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="35"/>
+      <c r="B47" s="35"/>
+      <c r="C47" s="35"/>
+      <c r="D47" s="35"/>
+      <c r="E47" s="35"/>
+      <c r="F47" s="35"/>
+      <c r="G47" s="35"/>
+      <c r="H47" s="35"/>
+      <c r="I47" s="35"/>
+      <c r="J47" s="35"/>
+      <c r="K47" s="35"/>
+      <c r="L47" s="35"/>
+      <c r="M47" s="35"/>
+      <c r="N47" s="35"/>
+      <c r="O47" s="35"/>
+    </row>
+    <row r="48" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I48" s="75" t="s">
+        <v>144</v>
+      </c>
+      <c r="K48" s="80"/>
+    </row>
+    <row r="49" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" spans="1:15" s="44" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="81" t="s">
+        <v>148</v>
+      </c>
+      <c r="B50" s="81"/>
+      <c r="C50" s="81"/>
+      <c r="D50" s="81"/>
+      <c r="E50" s="81"/>
+      <c r="F50" s="81"/>
+      <c r="G50" s="81"/>
+      <c r="H50" s="81"/>
+      <c r="I50" s="81"/>
+      <c r="J50" s="81"/>
+      <c r="K50" s="81"/>
+    </row>
+    <row r="51" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="35"/>
+      <c r="B51" s="35"/>
+      <c r="C51" s="35"/>
+      <c r="D51" s="35"/>
+      <c r="E51" s="35"/>
+      <c r="F51" s="35"/>
+      <c r="G51" s="35"/>
+      <c r="H51" s="35"/>
+      <c r="I51" s="35"/>
+      <c r="J51" s="35"/>
+      <c r="K51" s="35"/>
+      <c r="L51" s="35"/>
+      <c r="M51" s="35"/>
+      <c r="N51" s="35"/>
+      <c r="O51" s="35"/>
+    </row>
+    <row r="52" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="82" t="s">
+        <v>149</v>
+      </c>
+      <c r="B52" s="35"/>
+      <c r="C52" s="45"/>
+      <c r="D52" s="35"/>
+      <c r="E52" s="83" t="s">
+        <v>155</v>
+      </c>
+      <c r="F52" s="35"/>
+      <c r="G52" s="47"/>
+      <c r="H52" s="35"/>
+      <c r="I52" s="83" t="s">
+        <v>161</v>
+      </c>
+      <c r="J52" s="35"/>
+      <c r="K52" s="47"/>
+    </row>
+    <row r="53" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="35"/>
+      <c r="B53" s="35"/>
+      <c r="C53" s="35"/>
+      <c r="D53" s="35"/>
+      <c r="E53" s="35"/>
+      <c r="F53" s="35"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="35"/>
+      <c r="I53" s="35"/>
+      <c r="J53" s="35"/>
+      <c r="K53" s="35"/>
+    </row>
+    <row r="54" spans="1:15" s="44" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="82" t="s">
+        <v>150</v>
+      </c>
+      <c r="B54" s="35"/>
+      <c r="C54" s="49"/>
+      <c r="D54" s="35"/>
+      <c r="E54" s="82" t="s">
+        <v>156</v>
+      </c>
+      <c r="F54" s="35"/>
+      <c r="G54" s="49"/>
+      <c r="H54" s="35"/>
+      <c r="I54" s="82" t="s">
+        <v>162</v>
+      </c>
+      <c r="J54" s="35"/>
+      <c r="K54" s="49"/>
+    </row>
+    <row r="55" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="35"/>
+      <c r="B55" s="35"/>
+      <c r="C55" s="35"/>
+      <c r="D55" s="35"/>
+      <c r="E55" s="35"/>
+      <c r="F55" s="35"/>
+      <c r="G55" s="35"/>
+      <c r="H55" s="35"/>
+      <c r="I55" s="35"/>
+      <c r="J55" s="35"/>
+      <c r="K55" s="35"/>
+    </row>
+    <row r="56" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="82" t="s">
+        <v>151</v>
+      </c>
+      <c r="B56" s="35"/>
+      <c r="C56" s="49"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="82" t="s">
+        <v>157</v>
+      </c>
+      <c r="F56" s="35"/>
+      <c r="G56" s="49"/>
+      <c r="H56" s="35"/>
+      <c r="I56" s="82" t="s">
+        <v>163</v>
+      </c>
+      <c r="J56" s="35"/>
+      <c r="K56" s="49"/>
+    </row>
+    <row r="57" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="35"/>
+      <c r="B57" s="35"/>
+      <c r="C57" s="35"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="35"/>
+      <c r="G57" s="35"/>
+      <c r="H57" s="35"/>
+      <c r="I57" s="35"/>
+      <c r="J57" s="35"/>
+      <c r="K57" s="35"/>
+    </row>
+    <row r="58" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="82" t="s">
+        <v>152</v>
+      </c>
+      <c r="B58" s="35"/>
+      <c r="C58" s="49"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="82" t="s">
+        <v>158</v>
+      </c>
+      <c r="F58" s="35"/>
+      <c r="G58" s="49"/>
+      <c r="H58" s="35"/>
+      <c r="I58" s="82" t="s">
+        <v>164</v>
+      </c>
+      <c r="J58" s="35"/>
+      <c r="K58" s="49"/>
+    </row>
+    <row r="59" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="35"/>
+      <c r="B59" s="35"/>
+      <c r="C59" s="35"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="35"/>
+      <c r="H59" s="35"/>
+      <c r="I59" s="35"/>
+      <c r="J59" s="35"/>
+      <c r="K59" s="35"/>
+    </row>
+    <row r="60" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="82" t="s">
+        <v>153</v>
+      </c>
+      <c r="B60" s="35"/>
+      <c r="C60" s="45"/>
+      <c r="D60" s="35"/>
+      <c r="E60" s="83" t="s">
+        <v>159</v>
+      </c>
+      <c r="F60" s="35"/>
+      <c r="G60" s="47"/>
+      <c r="H60" s="35"/>
+      <c r="I60" s="83" t="s">
+        <v>165</v>
+      </c>
+      <c r="J60" s="35"/>
+      <c r="K60" s="47"/>
+    </row>
+    <row r="61" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="35"/>
+      <c r="B61" s="35"/>
+      <c r="C61" s="35"/>
+      <c r="D61" s="35"/>
+      <c r="E61" s="35"/>
+      <c r="F61" s="35"/>
+      <c r="G61" s="35"/>
+      <c r="H61" s="35"/>
+      <c r="I61" s="35"/>
+      <c r="J61" s="35"/>
+      <c r="K61" s="35"/>
+    </row>
+    <row r="62" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="82" t="s">
+        <v>154</v>
+      </c>
+      <c r="B62" s="35"/>
+      <c r="C62" s="45"/>
+      <c r="D62" s="35"/>
+      <c r="E62" s="84" t="s">
+        <v>160</v>
+      </c>
+      <c r="F62" s="35"/>
+      <c r="G62" s="45"/>
+      <c r="H62" s="35"/>
+      <c r="I62" s="84" t="s">
+        <v>166</v>
+      </c>
+      <c r="J62" s="35"/>
+      <c r="K62" s="45"/>
+    </row>
+    <row r="63" spans="1:15" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:15" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="65" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="66" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="68" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="69" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="70" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="71" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="72" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="73" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="74" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="75" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="76" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="77" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="78" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="79" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="80" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="81" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="82" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="83" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="84" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="85" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="86" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="87" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="88" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="89" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="90" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="91" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="92" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="93" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="94" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="95" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="96" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="97" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="98" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="99" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="100" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="101" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="102" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="103" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="104" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="105" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="106" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="107" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="108" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="109" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="110" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="111" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="112" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="113" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="114" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="115" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="116" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="117" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="118" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="119" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="120" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="121" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="122" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="123" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="124" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="125" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="126" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="127" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="128" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="129" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="130" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="131" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="132" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="133" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="134" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="135" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="136" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="137" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="138" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="139" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="140" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="141" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="142" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="143" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="144" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="145" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="146" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="147" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="148" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="149" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="150" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="151" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="152" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="153" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="154" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="155" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="156" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="157" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="158" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="159" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="160" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="161" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="162" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="163" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="164" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="165" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="166" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="167" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="168" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="169" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="170" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="171" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="172" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="173" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="174" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="175" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="176" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="A50:K50"/>
+    <mergeCell ref="M36:M38"/>
+    <mergeCell ref="M40:M42"/>
+    <mergeCell ref="M44:M46"/>
+    <mergeCell ref="O36:O38"/>
+    <mergeCell ref="O40:O42"/>
+    <mergeCell ref="O44:O46"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="M34:O34"/>
+    <mergeCell ref="I6:I10"/>
+    <mergeCell ref="I12:I16"/>
+    <mergeCell ref="K6:O10"/>
+    <mergeCell ref="K12:O16"/>
+    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="A18:C18"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA5F0923-2FA0-B442-B432-F0C48886CD46}">
   <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -957,7 +2920,7 @@
       <c r="A3" s="23"/>
     </row>
     <row r="4" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="34" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="10"/>
@@ -984,11 +2947,11 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="24"/>
+      <c r="A5" s="34"/>
       <c r="B5" s="10"/>
     </row>
     <row r="6" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A6" s="24"/>
+      <c r="A6" s="34"/>
       <c r="B6" s="10"/>
       <c r="C6" s="4" t="s">
         <v>27</v>
@@ -1010,41 +2973,28 @@
       </c>
     </row>
     <row r="7" spans="1:15" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="33"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="37"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="37"/>
-      <c r="N7" s="35"/>
-      <c r="O7" s="37"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="31"/>
     </row>
     <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="27"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="29"/>
+      <c r="A8" s="24"/>
+      <c r="B8" s="10"/>
     </row>
     <row r="9" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="34" t="s">
         <v>54</v>
       </c>
       <c r="B9" s="10"/>
@@ -1071,64 +3021,39 @@
       </c>
     </row>
     <row r="10" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="31"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="29"/>
+      <c r="A10" s="34"/>
+      <c r="B10" s="10"/>
     </row>
     <row r="11" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A11" s="31"/>
-      <c r="B11" s="28"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="30"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="29"/>
     </row>
     <row r="12" spans="1:15" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="33"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="37"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="37"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="29"/>
+      <c r="O12" s="31"/>
     </row>
     <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
+      <c r="A13" s="25"/>
       <c r="B13" s="11"/>
     </row>
     <row r="14" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="34" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="10"/>
@@ -1155,11 +3080,11 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="24"/>
+      <c r="A15" s="34"/>
       <c r="B15" s="10"/>
     </row>
     <row r="16" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A16" s="24"/>
+      <c r="A16" s="34"/>
       <c r="B16" s="10"/>
       <c r="C16" s="4" t="s">
         <v>26</v>
@@ -1184,11 +3109,11 @@
       </c>
     </row>
     <row r="17" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="24"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="10"/>
     </row>
     <row r="18" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A18" s="24"/>
+      <c r="A18" s="34"/>
       <c r="B18" s="10"/>
       <c r="C18" s="5" t="s">
         <v>68</v>
@@ -1201,41 +3126,30 @@
       <c r="O18" s="15"/>
     </row>
     <row r="19" spans="1:15" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="33"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="37"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="37"/>
-      <c r="L19" s="32"/>
-      <c r="M19" s="37"/>
-      <c r="N19" s="35"/>
-      <c r="O19" s="37"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="31"/>
+      <c r="N19" s="29"/>
+      <c r="O19" s="31"/>
     </row>
     <row r="20" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="38"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="36"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="29"/>
+      <c r="A20" s="32"/>
+      <c r="B20" s="33"/>
+      <c r="H20" s="30"/>
+      <c r="L20" s="30"/>
     </row>
     <row r="21" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="24" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="10"/>
@@ -1262,28 +3176,28 @@
       </c>
     </row>
     <row r="22" spans="1:15" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="33"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="37"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="37"/>
-      <c r="N22" s="35"/>
-      <c r="O22" s="37"/>
+      <c r="A22" s="27"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="31"/>
+      <c r="N22" s="29"/>
+      <c r="O22" s="31"/>
     </row>
     <row r="23" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="26"/>
+      <c r="A23" s="25"/>
       <c r="B23" s="11"/>
     </row>
     <row r="24" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="34" t="s">
         <v>32</v>
       </c>
       <c r="B24" s="10"/>
@@ -1310,11 +3224,11 @@
       </c>
     </row>
     <row r="25" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="24"/>
+      <c r="A25" s="34"/>
       <c r="B25" s="10"/>
     </row>
     <row r="26" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A26" s="24"/>
+      <c r="A26" s="34"/>
       <c r="B26" s="10"/>
       <c r="C26" s="5" t="s">
         <v>38</v>
@@ -1330,28 +3244,28 @@
       </c>
     </row>
     <row r="27" spans="1:15" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="33"/>
-      <c r="B27" s="34"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="35"/>
-      <c r="K27" s="37"/>
-      <c r="L27" s="35"/>
-      <c r="M27" s="37"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="37"/>
+      <c r="A27" s="27"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="31"/>
+      <c r="N27" s="29"/>
+      <c r="O27" s="31"/>
     </row>
     <row r="28" spans="1:15" ht="19" x14ac:dyDescent="0.25">
-      <c r="A28" s="26"/>
+      <c r="A28" s="25"/>
       <c r="B28" s="11"/>
     </row>
     <row r="29" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A29" s="24" t="s">
+      <c r="A29" s="34" t="s">
         <v>40</v>
       </c>
       <c r="B29" s="10"/>
@@ -1378,11 +3292,11 @@
       </c>
     </row>
     <row r="30" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="24"/>
+      <c r="A30" s="34"/>
       <c r="B30" s="10"/>
     </row>
     <row r="31" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A31" s="24"/>
+      <c r="A31" s="34"/>
       <c r="B31" s="10"/>
       <c r="C31" s="7" t="s">
         <v>45</v>
@@ -1392,28 +3306,28 @@
       </c>
     </row>
     <row r="32" spans="1:15" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="33"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="37"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="37"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="37"/>
-      <c r="J32" s="35"/>
-      <c r="K32" s="37"/>
-      <c r="L32" s="35"/>
-      <c r="M32" s="37"/>
-      <c r="N32" s="35"/>
-      <c r="O32" s="37"/>
+      <c r="A32" s="27"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="29"/>
+      <c r="O32" s="31"/>
     </row>
     <row r="33" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="26"/>
+      <c r="A33" s="25"/>
       <c r="B33" s="11"/>
     </row>
     <row r="34" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="34" t="s">
         <v>47</v>
       </c>
       <c r="B34" s="10"/>
@@ -1440,11 +3354,11 @@
       </c>
     </row>
     <row r="35" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="24"/>
+      <c r="A35" s="34"/>
       <c r="B35" s="10"/>
     </row>
     <row r="36" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A36" s="24"/>
+      <c r="A36" s="34"/>
       <c r="B36" s="10"/>
       <c r="C36" s="5" t="s">
         <v>7</v>
@@ -1466,21 +3380,21 @@
       </c>
     </row>
     <row r="37" spans="1:15" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="33"/>
-      <c r="B37" s="34"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="35"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="37"/>
-      <c r="J37" s="35"/>
-      <c r="K37" s="37"/>
-      <c r="L37" s="35"/>
-      <c r="M37" s="37"/>
-      <c r="N37" s="35"/>
-      <c r="O37" s="37"/>
+      <c r="A37" s="27"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="31"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="31"/>
+      <c r="N37" s="29"/>
+      <c r="O37" s="31"/>
     </row>
     <row r="40" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="G40" s="3" t="s">

--- a/images/2024-07-01-Omnissa-poc/Omnissa-adoption-map.xlsx
+++ b/images/2024-07-01-Omnissa-poc/Omnissa-adoption-map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mbeaugrand/github/blog/images/2024-07-01-Omnissa-poc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F60C2D4-17EA-0F48-B4B6-3640803DFF2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EDDFFF8-6D40-3F46-9589-B820A7ECD273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14480" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15680" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Company profile" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="168">
   <si>
     <t>Testing</t>
   </si>
@@ -522,6 +522,9 @@
   </si>
   <si>
     <t>AR headsets OEM</t>
+  </si>
+  <si>
+    <t>Vulnerability Defense</t>
   </si>
 </sst>
 </file>
@@ -894,7 +897,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -973,23 +976,71 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1000,79 +1051,58 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1087,43 +1117,10 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1586,1249 +1583,1262 @@
       <c r="N2" s="21"/>
       <c r="O2" s="22"/>
     </row>
-    <row r="3" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="43"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="43"/>
-    </row>
-    <row r="4" spans="1:15" s="44" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="39" t="s">
+    <row r="3" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="34"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
+      <c r="N3" s="34"/>
+      <c r="O3" s="34"/>
+    </row>
+    <row r="4" spans="1:15" s="36" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="81" t="s">
         <v>80</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39"/>
-      <c r="M4" s="39"/>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-    </row>
-    <row r="5" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="35"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="35"/>
-      <c r="M5" s="35"/>
-      <c r="N5" s="35"/>
-      <c r="O5" s="35"/>
-    </row>
-    <row r="6" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="38" t="s">
+      <c r="B4" s="81"/>
+      <c r="C4" s="81"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81"/>
+      <c r="L4" s="81"/>
+      <c r="M4" s="81"/>
+      <c r="N4" s="81"/>
+      <c r="O4" s="81"/>
+    </row>
+    <row r="5" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="34"/>
+    </row>
+    <row r="6" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="46" t="s">
+      <c r="B6" s="34"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="F6" s="35"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="48" t="s">
+      <c r="F6" s="34"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="J6" s="35"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="59"/>
-      <c r="M6" s="59"/>
-      <c r="N6" s="59"/>
-      <c r="O6" s="60"/>
-    </row>
-    <row r="7" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="35"/>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="61"/>
-    </row>
-    <row r="8" spans="1:15" s="44" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="38" t="s">
+      <c r="J6" s="34"/>
+      <c r="K6" s="63"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="65"/>
+    </row>
+    <row r="7" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="66"/>
+      <c r="L7" s="67"/>
+      <c r="M7" s="67"/>
+      <c r="N7" s="67"/>
+      <c r="O7" s="68"/>
+    </row>
+    <row r="8" spans="1:15" s="36" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="38" t="s">
+      <c r="B8" s="34"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="F8" s="35"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="36"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="61"/>
-    </row>
-    <row r="9" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="35"/>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="35"/>
-      <c r="K9" s="56"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="61"/>
-    </row>
-    <row r="10" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="38" t="s">
+      <c r="F8" s="34"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="67"/>
+      <c r="M8" s="67"/>
+      <c r="N8" s="67"/>
+      <c r="O8" s="68"/>
+    </row>
+    <row r="9" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="34"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="66"/>
+      <c r="L9" s="67"/>
+      <c r="M9" s="67"/>
+      <c r="N9" s="67"/>
+      <c r="O9" s="68"/>
+    </row>
+    <row r="10" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="38" t="s">
+      <c r="B10" s="34"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="F10" s="35"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="62"/>
-      <c r="L10" s="63"/>
-      <c r="M10" s="63"/>
-      <c r="N10" s="63"/>
-      <c r="O10" s="64"/>
-    </row>
-    <row r="11" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="35"/>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="35"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
-      <c r="N11" s="35"/>
-      <c r="O11" s="35"/>
-    </row>
-    <row r="12" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="38" t="s">
+      <c r="F10" s="34"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="34"/>
+      <c r="K10" s="69"/>
+      <c r="L10" s="70"/>
+      <c r="M10" s="70"/>
+      <c r="N10" s="70"/>
+      <c r="O10" s="71"/>
+    </row>
+    <row r="11" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="34"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="34"/>
+      <c r="L11" s="34"/>
+      <c r="M11" s="34"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="34"/>
+    </row>
+    <row r="12" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="38" t="s">
+      <c r="B12" s="34"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="F12" s="35"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="50" t="s">
+      <c r="F12" s="34"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="62" t="s">
         <v>91</v>
       </c>
-      <c r="J12" s="35"/>
-      <c r="K12" s="65"/>
-      <c r="L12" s="66"/>
-      <c r="M12" s="66"/>
-      <c r="N12" s="66"/>
-      <c r="O12" s="67"/>
-    </row>
-    <row r="13" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="35"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="35"/>
-      <c r="K13" s="57"/>
-      <c r="L13" s="37"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="68"/>
-    </row>
-    <row r="14" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="38" t="s">
+      <c r="J12" s="34"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="73"/>
+      <c r="M12" s="73"/>
+      <c r="N12" s="73"/>
+      <c r="O12" s="74"/>
+    </row>
+    <row r="13" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="34"/>
+      <c r="K13" s="75"/>
+      <c r="L13" s="76"/>
+      <c r="M13" s="76"/>
+      <c r="N13" s="76"/>
+      <c r="O13" s="77"/>
+    </row>
+    <row r="14" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="46" t="s">
+      <c r="B14" s="34"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="F14" s="35"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="50"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="57"/>
-      <c r="L14" s="37"/>
-      <c r="M14" s="37"/>
-      <c r="N14" s="37"/>
-      <c r="O14" s="68"/>
-    </row>
-    <row r="15" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="35"/>
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="57"/>
-      <c r="L15" s="37"/>
-      <c r="M15" s="37"/>
-      <c r="N15" s="37"/>
-      <c r="O15" s="68"/>
-    </row>
-    <row r="16" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="38" t="s">
+      <c r="F14" s="34"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="34"/>
+      <c r="K14" s="75"/>
+      <c r="L14" s="76"/>
+      <c r="M14" s="76"/>
+      <c r="N14" s="76"/>
+      <c r="O14" s="77"/>
+    </row>
+    <row r="15" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="34"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="75"/>
+      <c r="L15" s="76"/>
+      <c r="M15" s="76"/>
+      <c r="N15" s="76"/>
+      <c r="O15" s="77"/>
+    </row>
+    <row r="16" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="51" t="s">
+      <c r="B16" s="34"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="F16" s="35"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="69"/>
-      <c r="L16" s="70"/>
-      <c r="M16" s="70"/>
-      <c r="N16" s="70"/>
-      <c r="O16" s="71"/>
-    </row>
-    <row r="17" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="35"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="35"/>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="35"/>
-      <c r="O17" s="35"/>
-    </row>
-    <row r="18" spans="1:15" s="44" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="55" t="s">
+      <c r="F16" s="34"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="78"/>
+      <c r="L16" s="79"/>
+      <c r="M16" s="79"/>
+      <c r="N16" s="79"/>
+      <c r="O16" s="80"/>
+    </row>
+    <row r="17" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="34"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="34"/>
+    </row>
+    <row r="18" spans="1:15" s="36" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="59" t="s">
         <v>92</v>
       </c>
-      <c r="B18" s="55"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="55" t="s">
+      <c r="B18" s="59"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="59" t="s">
         <v>100</v>
       </c>
-      <c r="F18" s="55"/>
-      <c r="G18" s="55"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="55" t="s">
+      <c r="F18" s="59"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="59" t="s">
         <v>108</v>
       </c>
-      <c r="J18" s="55"/>
-      <c r="K18" s="55"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="55" t="s">
+      <c r="J18" s="59"/>
+      <c r="K18" s="59"/>
+      <c r="L18" s="34"/>
+      <c r="M18" s="59" t="s">
         <v>116</v>
       </c>
-      <c r="N18" s="55"/>
-      <c r="O18" s="55"/>
-    </row>
-    <row r="19" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="35"/>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="35"/>
-      <c r="L19" s="35"/>
-      <c r="M19" s="35"/>
-      <c r="N19" s="35"/>
-      <c r="O19" s="35"/>
-    </row>
-    <row r="20" spans="1:15" s="44" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="52" t="s">
+      <c r="N18" s="59"/>
+      <c r="O18" s="59"/>
+    </row>
+    <row r="19" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="34"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="34"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="34"/>
+    </row>
+    <row r="20" spans="1:15" s="36" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="B20" s="35"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="52" t="s">
+      <c r="B20" s="34"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="42" t="s">
         <v>101</v>
       </c>
-      <c r="F20" s="35"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="52" t="s">
+      <c r="F20" s="34"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="J20" s="35"/>
-      <c r="K20" s="49"/>
-      <c r="L20" s="35"/>
-      <c r="M20" s="52" t="s">
+      <c r="J20" s="34"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="34"/>
+      <c r="M20" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="N20" s="35"/>
-      <c r="O20" s="49"/>
-    </row>
-    <row r="21" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="35"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="35"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="35"/>
-    </row>
-    <row r="22" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="52" t="s">
+      <c r="N20" s="34"/>
+      <c r="O20" s="40"/>
+    </row>
+    <row r="21" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="34"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="34"/>
+    </row>
+    <row r="22" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="52" t="s">
+      <c r="B22" s="34"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="F22" s="35"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="52" t="s">
+      <c r="F22" s="34"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="J22" s="35"/>
-      <c r="K22" s="49"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="52" t="s">
+      <c r="J22" s="34"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="N22" s="35"/>
-      <c r="O22" s="49"/>
-    </row>
-    <row r="23" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="35"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="35"/>
-      <c r="K23" s="35"/>
-      <c r="L23" s="35"/>
-      <c r="M23" s="35"/>
-      <c r="N23" s="35"/>
-      <c r="O23" s="35"/>
-    </row>
-    <row r="24" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="52" t="s">
+      <c r="N22" s="34"/>
+      <c r="O22" s="40"/>
+    </row>
+    <row r="23" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="34"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="34"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="34"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="34"/>
+      <c r="O23" s="34"/>
+    </row>
+    <row r="24" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="42" t="s">
         <v>95</v>
       </c>
-      <c r="B24" s="35"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="53" t="s">
+      <c r="B24" s="34"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="F24" s="35"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="53" t="s">
+      <c r="F24" s="34"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="J24" s="35"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="54" t="s">
+      <c r="J24" s="34"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="34"/>
+      <c r="M24" s="44" t="s">
         <v>119</v>
       </c>
-      <c r="N24" s="35"/>
-      <c r="O24" s="45"/>
-    </row>
-    <row r="25" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="35"/>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="35"/>
-      <c r="L25" s="35"/>
-      <c r="M25" s="35"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="35"/>
-    </row>
-    <row r="26" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="52" t="s">
+      <c r="N24" s="34"/>
+      <c r="O24" s="37"/>
+    </row>
+    <row r="25" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="34"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="34"/>
+      <c r="L25" s="34"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="34"/>
+      <c r="O25" s="34"/>
+    </row>
+    <row r="26" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="B26" s="35"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="53" t="s">
+      <c r="B26" s="34"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="F26" s="35"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="52" t="s">
+      <c r="F26" s="34"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="J26" s="35"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="52" t="s">
+      <c r="J26" s="34"/>
+      <c r="K26" s="40"/>
+      <c r="L26" s="34"/>
+      <c r="M26" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="N26" s="35"/>
-      <c r="O26" s="49"/>
-    </row>
-    <row r="27" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="35"/>
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="35"/>
-      <c r="K27" s="35"/>
-      <c r="L27" s="35"/>
-      <c r="M27" s="35"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="35"/>
-    </row>
-    <row r="28" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="52" t="s">
+      <c r="N26" s="34"/>
+      <c r="O26" s="40"/>
+    </row>
+    <row r="27" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="34"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="34"/>
+      <c r="K27" s="34"/>
+      <c r="L27" s="34"/>
+      <c r="M27" s="34"/>
+      <c r="N27" s="34"/>
+      <c r="O27" s="34"/>
+    </row>
+    <row r="28" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="B28" s="35"/>
-      <c r="C28" s="49"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="52" t="s">
+      <c r="B28" s="34"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="42" t="s">
         <v>105</v>
       </c>
-      <c r="F28" s="35"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="52" t="s">
+      <c r="F28" s="34"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="J28" s="35"/>
-      <c r="K28" s="49"/>
-      <c r="L28" s="35"/>
-      <c r="M28" s="52" t="s">
+      <c r="J28" s="34"/>
+      <c r="K28" s="40"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="42" t="s">
         <v>121</v>
       </c>
-      <c r="N28" s="35"/>
-      <c r="O28" s="49"/>
-    </row>
-    <row r="29" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="35"/>
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="35"/>
-      <c r="J29" s="35"/>
-      <c r="K29" s="35"/>
-      <c r="L29" s="35"/>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
-      <c r="O29" s="35"/>
-    </row>
-    <row r="30" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="52" t="s">
+      <c r="N28" s="34"/>
+      <c r="O28" s="40"/>
+    </row>
+    <row r="29" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="34"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="34"/>
+      <c r="K29" s="34"/>
+      <c r="L29" s="34"/>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
+      <c r="O29" s="34"/>
+    </row>
+    <row r="30" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="B30" s="35"/>
-      <c r="C30" s="49"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="52" t="s">
+      <c r="B30" s="34"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="42" t="s">
         <v>106</v>
       </c>
-      <c r="F30" s="35"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="52" t="s">
+      <c r="F30" s="34"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="J30" s="35"/>
-      <c r="K30" s="49"/>
-      <c r="L30" s="35"/>
-      <c r="M30" s="52" t="s">
+      <c r="J30" s="34"/>
+      <c r="K30" s="40"/>
+      <c r="L30" s="34"/>
+      <c r="M30" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="N30" s="35"/>
-      <c r="O30" s="49"/>
-    </row>
-    <row r="31" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="35"/>
-      <c r="B31" s="35"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="35"/>
-      <c r="J31" s="35"/>
-      <c r="K31" s="35"/>
-      <c r="L31" s="35"/>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="35"/>
-    </row>
-    <row r="32" spans="1:15" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="52" t="s">
+      <c r="N30" s="34"/>
+      <c r="O30" s="40"/>
+    </row>
+    <row r="31" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="34"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="34"/>
+      <c r="K31" s="34"/>
+      <c r="L31" s="34"/>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
+      <c r="O31" s="34"/>
+    </row>
+    <row r="32" spans="1:15" s="36" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="42" t="s">
         <v>99</v>
       </c>
-      <c r="B32" s="35"/>
-      <c r="C32" s="49"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="52" t="s">
+      <c r="B32" s="34"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="42" t="s">
         <v>107</v>
       </c>
-      <c r="F32" s="35"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="52" t="s">
+      <c r="F32" s="34"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="J32" s="35"/>
-      <c r="K32" s="49"/>
-      <c r="L32" s="35"/>
-      <c r="M32" s="52" t="s">
+      <c r="J32" s="34"/>
+      <c r="K32" s="40"/>
+      <c r="L32" s="34"/>
+      <c r="M32" s="42" t="s">
         <v>123</v>
       </c>
-      <c r="N32" s="35"/>
-      <c r="O32" s="49"/>
-    </row>
-    <row r="33" spans="1:15" s="44" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="35"/>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="35"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="35"/>
-      <c r="J33" s="35"/>
-      <c r="K33" s="35"/>
-      <c r="L33" s="35"/>
-      <c r="M33" s="35"/>
-      <c r="N33" s="35"/>
-      <c r="O33" s="35"/>
-    </row>
-    <row r="34" spans="1:15" s="44" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="72" t="s">
+      <c r="N32" s="34"/>
+      <c r="O32" s="40"/>
+    </row>
+    <row r="33" spans="1:15" s="36" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="34"/>
+      <c r="B33" s="34"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="34"/>
+      <c r="K33" s="34"/>
+      <c r="L33" s="34"/>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
+      <c r="O33" s="34"/>
+    </row>
+    <row r="34" spans="1:15" s="36" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="60" t="s">
         <v>124</v>
       </c>
-      <c r="B34" s="72"/>
-      <c r="C34" s="72"/>
-      <c r="D34" s="35"/>
-      <c r="E34" s="72" t="s">
+      <c r="B34" s="60"/>
+      <c r="C34" s="60"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="60" t="s">
         <v>125</v>
       </c>
-      <c r="F34" s="72"/>
-      <c r="G34" s="72"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="72" t="s">
+      <c r="F34" s="60"/>
+      <c r="G34" s="60"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="60" t="s">
         <v>126</v>
       </c>
-      <c r="J34" s="72"/>
-      <c r="K34" s="72"/>
-      <c r="L34" s="35"/>
-      <c r="M34" s="72" t="s">
+      <c r="J34" s="60"/>
+      <c r="K34" s="60"/>
+      <c r="L34" s="34"/>
+      <c r="M34" s="60" t="s">
         <v>127</v>
       </c>
-      <c r="N34" s="72"/>
-      <c r="O34" s="72"/>
-    </row>
-    <row r="35" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="35"/>
-      <c r="B35" s="35"/>
-      <c r="C35" s="35"/>
-      <c r="D35" s="35"/>
-      <c r="E35" s="35"/>
-      <c r="F35" s="35"/>
-      <c r="G35" s="35"/>
-      <c r="H35" s="35"/>
-      <c r="I35" s="35"/>
-      <c r="J35" s="35"/>
-      <c r="K35" s="35"/>
-      <c r="L35" s="35"/>
-      <c r="M35" s="35"/>
-      <c r="N35" s="35"/>
-      <c r="O35" s="35"/>
-    </row>
-    <row r="36" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="77" t="s">
+      <c r="N34" s="60"/>
+      <c r="O34" s="60"/>
+    </row>
+    <row r="35" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="34"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="34"/>
+      <c r="I35" s="34"/>
+      <c r="J35" s="34"/>
+      <c r="K35" s="34"/>
+      <c r="L35" s="34"/>
+      <c r="M35" s="34"/>
+      <c r="N35" s="34"/>
+      <c r="O35" s="34"/>
+    </row>
+    <row r="36" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="35"/>
-      <c r="C36" s="47"/>
-      <c r="D36" s="35"/>
-      <c r="E36" s="78" t="s">
+      <c r="B36" s="34"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="45" t="s">
         <v>132</v>
       </c>
-      <c r="F36" s="35"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="78" t="s">
+      <c r="F36" s="34"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="34"/>
+      <c r="I36" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="J36" s="35"/>
-      <c r="K36" s="47"/>
-      <c r="L36" s="35"/>
-      <c r="M36" s="73" t="s">
+      <c r="J36" s="34"/>
+      <c r="K36" s="39"/>
+      <c r="L36" s="34"/>
+      <c r="M36" s="54" t="s">
         <v>145</v>
       </c>
-      <c r="N36" s="35"/>
-      <c r="O36" s="40"/>
-    </row>
-    <row r="37" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="35"/>
-      <c r="B37" s="35"/>
-      <c r="C37" s="35"/>
-      <c r="D37" s="35"/>
-      <c r="E37" s="35"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="35"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="35"/>
-      <c r="J37" s="35"/>
-      <c r="K37" s="35"/>
-      <c r="L37" s="35"/>
-      <c r="M37" s="73"/>
-      <c r="N37" s="35"/>
-      <c r="O37" s="41"/>
-    </row>
-    <row r="38" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="77" t="s">
+      <c r="N36" s="34"/>
+      <c r="O36" s="56"/>
+    </row>
+    <row r="37" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="34"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="34"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="34"/>
+      <c r="I37" s="34"/>
+      <c r="J37" s="34"/>
+      <c r="K37" s="34"/>
+      <c r="L37" s="34"/>
+      <c r="M37" s="54"/>
+      <c r="N37" s="34"/>
+      <c r="O37" s="57"/>
+    </row>
+    <row r="38" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="B38" s="35"/>
-      <c r="C38" s="49"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="77" t="s">
+      <c r="B38" s="34"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="F38" s="35"/>
-      <c r="G38" s="49"/>
-      <c r="H38" s="35"/>
-      <c r="I38" s="77" t="s">
+      <c r="F38" s="34"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="34"/>
+      <c r="I38" s="46" t="s">
         <v>139</v>
       </c>
-      <c r="J38" s="35"/>
-      <c r="K38" s="49"/>
-      <c r="L38" s="35"/>
-      <c r="M38" s="73"/>
-      <c r="N38" s="35"/>
-      <c r="O38" s="42"/>
-    </row>
-    <row r="39" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="35"/>
-      <c r="B39" s="35"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="35"/>
-      <c r="F39" s="35"/>
-      <c r="G39" s="35"/>
-      <c r="H39" s="35"/>
-      <c r="I39" s="35"/>
-      <c r="J39" s="35"/>
-      <c r="K39" s="35"/>
-      <c r="L39" s="35"/>
-      <c r="M39" s="35"/>
-      <c r="N39" s="35"/>
-      <c r="O39" s="35"/>
-    </row>
-    <row r="40" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="77" t="s">
+      <c r="J38" s="34"/>
+      <c r="K38" s="40"/>
+      <c r="L38" s="34"/>
+      <c r="M38" s="54"/>
+      <c r="N38" s="34"/>
+      <c r="O38" s="58"/>
+    </row>
+    <row r="39" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="34"/>
+      <c r="B39" s="34"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="34"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="34"/>
+      <c r="I39" s="34"/>
+      <c r="J39" s="34"/>
+      <c r="K39" s="34"/>
+      <c r="L39" s="34"/>
+      <c r="M39" s="34"/>
+      <c r="N39" s="34"/>
+      <c r="O39" s="34"/>
+    </row>
+    <row r="40" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="B40" s="35"/>
-      <c r="C40" s="49"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="77" t="s">
+      <c r="B40" s="34"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="F40" s="35"/>
-      <c r="G40" s="49"/>
-      <c r="H40" s="35"/>
-      <c r="I40" s="76" t="s">
+      <c r="F40" s="34"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="34"/>
+      <c r="I40" s="47" t="s">
         <v>140</v>
       </c>
-      <c r="J40" s="35"/>
-      <c r="K40" s="79"/>
-      <c r="L40" s="35"/>
-      <c r="M40" s="73" t="s">
+      <c r="J40" s="34"/>
+      <c r="K40" s="48"/>
+      <c r="L40" s="34"/>
+      <c r="M40" s="54" t="s">
         <v>146</v>
       </c>
-      <c r="N40" s="35"/>
-      <c r="O40" s="40"/>
-    </row>
-    <row r="41" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="35"/>
-      <c r="B41" s="35"/>
-      <c r="C41" s="35"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="35"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="35"/>
-      <c r="H41" s="35"/>
-      <c r="I41" s="35"/>
-      <c r="J41" s="35"/>
-      <c r="K41" s="35"/>
-      <c r="L41" s="35"/>
-      <c r="M41" s="73"/>
-      <c r="N41" s="35"/>
-      <c r="O41" s="41"/>
-    </row>
-    <row r="42" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="75" t="s">
+      <c r="N40" s="34"/>
+      <c r="O40" s="56"/>
+    </row>
+    <row r="41" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="34"/>
+      <c r="B41" s="34"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="34"/>
+      <c r="H41" s="34"/>
+      <c r="I41" s="34"/>
+      <c r="J41" s="34"/>
+      <c r="K41" s="34"/>
+      <c r="L41" s="34"/>
+      <c r="M41" s="54"/>
+      <c r="N41" s="34"/>
+      <c r="O41" s="57"/>
+    </row>
+    <row r="42" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="B42" s="43"/>
-      <c r="C42" s="49"/>
-      <c r="D42" s="43"/>
-      <c r="E42" s="75" t="s">
+      <c r="B42" s="34"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="46" t="s">
         <v>135</v>
       </c>
-      <c r="F42" s="43"/>
-      <c r="G42" s="49"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="75" t="s">
+      <c r="F42" s="34"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="34"/>
+      <c r="I42" s="46" t="s">
         <v>141</v>
       </c>
-      <c r="J42" s="43"/>
-      <c r="K42" s="49"/>
-      <c r="L42" s="43"/>
-      <c r="M42" s="73"/>
-      <c r="N42" s="43"/>
-      <c r="O42" s="42"/>
-    </row>
-    <row r="43" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="35"/>
-      <c r="B43" s="35"/>
-      <c r="C43" s="35"/>
-      <c r="D43" s="35"/>
-      <c r="E43" s="35"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="35"/>
-      <c r="H43" s="35"/>
-      <c r="I43" s="35"/>
-      <c r="J43" s="35"/>
-      <c r="K43" s="35"/>
-      <c r="L43" s="35"/>
-      <c r="M43" s="35"/>
-      <c r="N43" s="35"/>
-      <c r="O43" s="35"/>
-    </row>
-    <row r="44" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="75" t="s">
+      <c r="J42" s="34"/>
+      <c r="K42" s="40"/>
+      <c r="L42" s="34"/>
+      <c r="M42" s="54"/>
+      <c r="N42" s="34"/>
+      <c r="O42" s="58"/>
+    </row>
+    <row r="43" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="34"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="34"/>
+      <c r="K43" s="34"/>
+      <c r="L43" s="34"/>
+      <c r="M43" s="34"/>
+      <c r="N43" s="34"/>
+      <c r="O43" s="34"/>
+    </row>
+    <row r="44" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="B44" s="43"/>
-      <c r="C44" s="49"/>
-      <c r="D44" s="43"/>
-      <c r="E44" s="75" t="s">
+      <c r="B44" s="34"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="46" t="s">
         <v>136</v>
       </c>
-      <c r="F44" s="43"/>
-      <c r="G44" s="49"/>
-      <c r="H44" s="43"/>
-      <c r="I44" s="75" t="s">
+      <c r="F44" s="34"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="34"/>
+      <c r="I44" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="J44" s="43"/>
-      <c r="K44" s="49"/>
-      <c r="L44" s="43"/>
-      <c r="M44" s="74" t="s">
+      <c r="J44" s="34"/>
+      <c r="K44" s="40"/>
+      <c r="L44" s="34"/>
+      <c r="M44" s="55" t="s">
         <v>147</v>
       </c>
-      <c r="N44" s="43"/>
-      <c r="O44" s="40"/>
-    </row>
-    <row r="45" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="35"/>
-      <c r="B45" s="35"/>
-      <c r="C45" s="35"/>
-      <c r="D45" s="35"/>
-      <c r="E45" s="35"/>
-      <c r="F45" s="35"/>
-      <c r="G45" s="35"/>
-      <c r="H45" s="35"/>
-      <c r="I45" s="35"/>
-      <c r="J45" s="35"/>
-      <c r="K45" s="35"/>
-      <c r="L45" s="35"/>
-      <c r="M45" s="74"/>
-      <c r="N45" s="35"/>
-      <c r="O45" s="41"/>
-    </row>
-    <row r="46" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="75" t="s">
+      <c r="N44" s="34"/>
+      <c r="O44" s="56"/>
+    </row>
+    <row r="45" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="34"/>
+      <c r="B45" s="34"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="34"/>
+      <c r="F45" s="34"/>
+      <c r="G45" s="34"/>
+      <c r="H45" s="34"/>
+      <c r="I45" s="34"/>
+      <c r="J45" s="34"/>
+      <c r="K45" s="34"/>
+      <c r="L45" s="34"/>
+      <c r="M45" s="55"/>
+      <c r="N45" s="34"/>
+      <c r="O45" s="57"/>
+    </row>
+    <row r="46" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="B46" s="43"/>
-      <c r="C46" s="49"/>
-      <c r="D46" s="43"/>
-      <c r="E46" s="75" t="s">
+      <c r="B46" s="34"/>
+      <c r="C46" s="40"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="46" t="s">
         <v>137</v>
       </c>
-      <c r="F46" s="43"/>
-      <c r="G46" s="49"/>
-      <c r="H46" s="43"/>
-      <c r="I46" s="75" t="s">
+      <c r="F46" s="34"/>
+      <c r="G46" s="40"/>
+      <c r="H46" s="34"/>
+      <c r="I46" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="J46" s="43"/>
-      <c r="K46" s="49"/>
-      <c r="L46" s="43"/>
-      <c r="M46" s="74"/>
-      <c r="N46" s="43"/>
-      <c r="O46" s="42"/>
-    </row>
-    <row r="47" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="35"/>
-      <c r="B47" s="35"/>
-      <c r="C47" s="35"/>
-      <c r="D47" s="35"/>
-      <c r="E47" s="35"/>
-      <c r="F47" s="35"/>
-      <c r="G47" s="35"/>
-      <c r="H47" s="35"/>
-      <c r="I47" s="35"/>
-      <c r="J47" s="35"/>
-      <c r="K47" s="35"/>
-      <c r="L47" s="35"/>
-      <c r="M47" s="35"/>
-      <c r="N47" s="35"/>
-      <c r="O47" s="35"/>
-    </row>
-    <row r="48" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I48" s="75" t="s">
+      <c r="J46" s="34"/>
+      <c r="K46" s="40"/>
+      <c r="L46" s="34"/>
+      <c r="M46" s="55"/>
+      <c r="N46" s="34"/>
+      <c r="O46" s="58"/>
+    </row>
+    <row r="47" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="34"/>
+      <c r="B47" s="34"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="34"/>
+      <c r="F47" s="34"/>
+      <c r="G47" s="34"/>
+      <c r="H47" s="34"/>
+      <c r="I47" s="34"/>
+      <c r="J47" s="34"/>
+      <c r="K47" s="34"/>
+      <c r="L47" s="34"/>
+      <c r="M47" s="34"/>
+      <c r="N47" s="34"/>
+      <c r="O47" s="34"/>
+    </row>
+    <row r="48" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I48" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="K48" s="80"/>
-    </row>
-    <row r="49" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" spans="1:15" s="44" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="81" t="s">
+      <c r="K48" s="49"/>
+    </row>
+    <row r="49" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" spans="1:15" s="36" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="53" t="s">
         <v>148</v>
       </c>
-      <c r="B50" s="81"/>
-      <c r="C50" s="81"/>
-      <c r="D50" s="81"/>
-      <c r="E50" s="81"/>
-      <c r="F50" s="81"/>
-      <c r="G50" s="81"/>
-      <c r="H50" s="81"/>
-      <c r="I50" s="81"/>
-      <c r="J50" s="81"/>
-      <c r="K50" s="81"/>
-    </row>
-    <row r="51" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="35"/>
-      <c r="B51" s="35"/>
-      <c r="C51" s="35"/>
-      <c r="D51" s="35"/>
-      <c r="E51" s="35"/>
-      <c r="F51" s="35"/>
-      <c r="G51" s="35"/>
-      <c r="H51" s="35"/>
-      <c r="I51" s="35"/>
-      <c r="J51" s="35"/>
-      <c r="K51" s="35"/>
-      <c r="L51" s="35"/>
-      <c r="M51" s="35"/>
-      <c r="N51" s="35"/>
-      <c r="O51" s="35"/>
-    </row>
-    <row r="52" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="82" t="s">
+      <c r="B50" s="53"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="53"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="53"/>
+      <c r="G50" s="53"/>
+      <c r="H50" s="53"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="53"/>
+    </row>
+    <row r="51" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="34"/>
+      <c r="B51" s="34"/>
+      <c r="C51" s="34"/>
+      <c r="D51" s="34"/>
+      <c r="E51" s="34"/>
+      <c r="F51" s="34"/>
+      <c r="G51" s="34"/>
+      <c r="H51" s="34"/>
+      <c r="I51" s="34"/>
+      <c r="J51" s="34"/>
+      <c r="K51" s="34"/>
+      <c r="L51" s="34"/>
+      <c r="M51" s="34"/>
+      <c r="N51" s="34"/>
+      <c r="O51" s="34"/>
+    </row>
+    <row r="52" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="50" t="s">
         <v>149</v>
       </c>
-      <c r="B52" s="35"/>
-      <c r="C52" s="45"/>
-      <c r="D52" s="35"/>
-      <c r="E52" s="83" t="s">
+      <c r="B52" s="34"/>
+      <c r="C52" s="37"/>
+      <c r="D52" s="34"/>
+      <c r="E52" s="51" t="s">
         <v>155</v>
       </c>
-      <c r="F52" s="35"/>
-      <c r="G52" s="47"/>
-      <c r="H52" s="35"/>
-      <c r="I52" s="83" t="s">
+      <c r="F52" s="34"/>
+      <c r="G52" s="39"/>
+      <c r="H52" s="34"/>
+      <c r="I52" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="J52" s="35"/>
-      <c r="K52" s="47"/>
-    </row>
-    <row r="53" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="35"/>
-      <c r="B53" s="35"/>
-      <c r="C53" s="35"/>
-      <c r="D53" s="35"/>
-      <c r="E53" s="35"/>
-      <c r="F53" s="35"/>
-      <c r="G53" s="35"/>
-      <c r="H53" s="35"/>
-      <c r="I53" s="35"/>
-      <c r="J53" s="35"/>
-      <c r="K53" s="35"/>
-    </row>
-    <row r="54" spans="1:15" s="44" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="82" t="s">
+      <c r="J52" s="34"/>
+      <c r="K52" s="39"/>
+    </row>
+    <row r="53" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="34"/>
+      <c r="B53" s="34"/>
+      <c r="C53" s="34"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="34"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="34"/>
+      <c r="H53" s="34"/>
+      <c r="I53" s="34"/>
+      <c r="J53" s="34"/>
+      <c r="K53" s="34"/>
+    </row>
+    <row r="54" spans="1:15" s="36" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="50" t="s">
         <v>150</v>
       </c>
-      <c r="B54" s="35"/>
-      <c r="C54" s="49"/>
-      <c r="D54" s="35"/>
-      <c r="E54" s="82" t="s">
+      <c r="B54" s="34"/>
+      <c r="C54" s="40"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="50" t="s">
         <v>156</v>
       </c>
-      <c r="F54" s="35"/>
-      <c r="G54" s="49"/>
-      <c r="H54" s="35"/>
-      <c r="I54" s="82" t="s">
+      <c r="F54" s="34"/>
+      <c r="G54" s="40"/>
+      <c r="H54" s="34"/>
+      <c r="I54" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="J54" s="35"/>
-      <c r="K54" s="49"/>
-    </row>
-    <row r="55" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="35"/>
-      <c r="B55" s="35"/>
-      <c r="C55" s="35"/>
-      <c r="D55" s="35"/>
-      <c r="E55" s="35"/>
-      <c r="F55" s="35"/>
-      <c r="G55" s="35"/>
-      <c r="H55" s="35"/>
-      <c r="I55" s="35"/>
-      <c r="J55" s="35"/>
-      <c r="K55" s="35"/>
-    </row>
-    <row r="56" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="82" t="s">
+      <c r="J54" s="34"/>
+      <c r="K54" s="40"/>
+    </row>
+    <row r="55" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="34"/>
+      <c r="B55" s="34"/>
+      <c r="C55" s="34"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="34"/>
+      <c r="F55" s="34"/>
+      <c r="G55" s="34"/>
+      <c r="H55" s="34"/>
+      <c r="I55" s="34"/>
+      <c r="J55" s="34"/>
+      <c r="K55" s="34"/>
+    </row>
+    <row r="56" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="50" t="s">
         <v>151</v>
       </c>
-      <c r="B56" s="35"/>
-      <c r="C56" s="49"/>
-      <c r="D56" s="35"/>
-      <c r="E56" s="82" t="s">
+      <c r="B56" s="34"/>
+      <c r="C56" s="40"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="50" t="s">
         <v>157</v>
       </c>
-      <c r="F56" s="35"/>
-      <c r="G56" s="49"/>
-      <c r="H56" s="35"/>
-      <c r="I56" s="82" t="s">
+      <c r="F56" s="34"/>
+      <c r="G56" s="40"/>
+      <c r="H56" s="34"/>
+      <c r="I56" s="50" t="s">
         <v>163</v>
       </c>
-      <c r="J56" s="35"/>
-      <c r="K56" s="49"/>
-    </row>
-    <row r="57" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="35"/>
-      <c r="B57" s="35"/>
-      <c r="C57" s="35"/>
-      <c r="D57" s="35"/>
-      <c r="E57" s="35"/>
-      <c r="F57" s="35"/>
-      <c r="G57" s="35"/>
-      <c r="H57" s="35"/>
-      <c r="I57" s="35"/>
-      <c r="J57" s="35"/>
-      <c r="K57" s="35"/>
-    </row>
-    <row r="58" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="82" t="s">
+      <c r="J56" s="34"/>
+      <c r="K56" s="40"/>
+    </row>
+    <row r="57" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="34"/>
+      <c r="B57" s="34"/>
+      <c r="C57" s="34"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="34"/>
+      <c r="F57" s="34"/>
+      <c r="G57" s="34"/>
+      <c r="H57" s="34"/>
+      <c r="I57" s="34"/>
+      <c r="J57" s="34"/>
+      <c r="K57" s="34"/>
+    </row>
+    <row r="58" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="50" t="s">
         <v>152</v>
       </c>
-      <c r="B58" s="35"/>
-      <c r="C58" s="49"/>
-      <c r="D58" s="35"/>
-      <c r="E58" s="82" t="s">
+      <c r="B58" s="34"/>
+      <c r="C58" s="40"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="50" t="s">
         <v>158</v>
       </c>
-      <c r="F58" s="35"/>
-      <c r="G58" s="49"/>
-      <c r="H58" s="35"/>
-      <c r="I58" s="82" t="s">
+      <c r="F58" s="34"/>
+      <c r="G58" s="40"/>
+      <c r="H58" s="34"/>
+      <c r="I58" s="50" t="s">
         <v>164</v>
       </c>
-      <c r="J58" s="35"/>
-      <c r="K58" s="49"/>
-    </row>
-    <row r="59" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="35"/>
-      <c r="B59" s="35"/>
-      <c r="C59" s="35"/>
-      <c r="D59" s="35"/>
-      <c r="E59" s="35"/>
-      <c r="F59" s="35"/>
-      <c r="G59" s="35"/>
-      <c r="H59" s="35"/>
-      <c r="I59" s="35"/>
-      <c r="J59" s="35"/>
-      <c r="K59" s="35"/>
-    </row>
-    <row r="60" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="82" t="s">
+      <c r="J58" s="34"/>
+      <c r="K58" s="40"/>
+    </row>
+    <row r="59" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="34"/>
+      <c r="B59" s="34"/>
+      <c r="C59" s="34"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="34"/>
+      <c r="F59" s="34"/>
+      <c r="G59" s="34"/>
+      <c r="H59" s="34"/>
+      <c r="I59" s="34"/>
+      <c r="J59" s="34"/>
+      <c r="K59" s="34"/>
+    </row>
+    <row r="60" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="50" t="s">
         <v>153</v>
       </c>
-      <c r="B60" s="35"/>
-      <c r="C60" s="45"/>
-      <c r="D60" s="35"/>
-      <c r="E60" s="83" t="s">
+      <c r="B60" s="34"/>
+      <c r="C60" s="37"/>
+      <c r="D60" s="34"/>
+      <c r="E60" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="F60" s="35"/>
-      <c r="G60" s="47"/>
-      <c r="H60" s="35"/>
-      <c r="I60" s="83" t="s">
+      <c r="F60" s="34"/>
+      <c r="G60" s="39"/>
+      <c r="H60" s="34"/>
+      <c r="I60" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="J60" s="35"/>
-      <c r="K60" s="47"/>
-    </row>
-    <row r="61" spans="1:15" s="44" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="35"/>
-      <c r="B61" s="35"/>
-      <c r="C61" s="35"/>
-      <c r="D61" s="35"/>
-      <c r="E61" s="35"/>
-      <c r="F61" s="35"/>
-      <c r="G61" s="35"/>
-      <c r="H61" s="35"/>
-      <c r="I61" s="35"/>
-      <c r="J61" s="35"/>
-      <c r="K61" s="35"/>
-    </row>
-    <row r="62" spans="1:15" s="44" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="82" t="s">
+      <c r="J60" s="34"/>
+      <c r="K60" s="39"/>
+    </row>
+    <row r="61" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="34"/>
+      <c r="B61" s="34"/>
+      <c r="C61" s="34"/>
+      <c r="D61" s="34"/>
+      <c r="E61" s="34"/>
+      <c r="F61" s="34"/>
+      <c r="G61" s="34"/>
+      <c r="H61" s="34"/>
+      <c r="I61" s="34"/>
+      <c r="J61" s="34"/>
+      <c r="K61" s="34"/>
+    </row>
+    <row r="62" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="50" t="s">
         <v>154</v>
       </c>
-      <c r="B62" s="35"/>
-      <c r="C62" s="45"/>
-      <c r="D62" s="35"/>
-      <c r="E62" s="84" t="s">
+      <c r="B62" s="34"/>
+      <c r="C62" s="37"/>
+      <c r="D62" s="34"/>
+      <c r="E62" s="52" t="s">
         <v>160</v>
       </c>
-      <c r="F62" s="35"/>
-      <c r="G62" s="45"/>
-      <c r="H62" s="35"/>
-      <c r="I62" s="84" t="s">
+      <c r="F62" s="34"/>
+      <c r="G62" s="37"/>
+      <c r="H62" s="34"/>
+      <c r="I62" s="52" t="s">
         <v>166</v>
       </c>
-      <c r="J62" s="35"/>
-      <c r="K62" s="45"/>
-    </row>
-    <row r="63" spans="1:15" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="1:15" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="65" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="66" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="67" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="68" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="69" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="70" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="71" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="72" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="73" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="74" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="75" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="76" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="77" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="78" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="79" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="80" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="81" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="82" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="83" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="84" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="85" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="86" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="87" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="88" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="89" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="90" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="91" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="92" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="93" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="94" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="95" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="96" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="97" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="98" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="99" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="100" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="101" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="102" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="103" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="104" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="105" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="106" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="107" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="108" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="109" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="110" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="111" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="112" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="113" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="114" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="115" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="116" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="117" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="118" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="119" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="120" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="121" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="122" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="123" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="124" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="125" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="126" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="127" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="128" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="129" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="130" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="131" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="132" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="133" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="134" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="135" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="136" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="137" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="138" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="139" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="140" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="141" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="142" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="143" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="144" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="145" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="146" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="147" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="148" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="149" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="150" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="151" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="152" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="153" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="154" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="155" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="156" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="157" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="158" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="159" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="160" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="161" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="162" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="163" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="164" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="165" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="166" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="167" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="168" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="169" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="170" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="171" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="172" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="173" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="174" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="175" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="176" s="44" customFormat="1" x14ac:dyDescent="0.2"/>
+      <c r="J62" s="34"/>
+      <c r="K62" s="37"/>
+    </row>
+    <row r="63" spans="1:15" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:15" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="65" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="66" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="68" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="69" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="70" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="71" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="72" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="73" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="74" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="75" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="76" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="77" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="78" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="79" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="80" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="81" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="82" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="83" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="84" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="85" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="86" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="87" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="88" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="89" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="90" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="91" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="92" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="93" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="94" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="95" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="96" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="97" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="98" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="99" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="100" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="101" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="102" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="103" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="104" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="105" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="106" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="107" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="108" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="109" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="110" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="111" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="112" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="113" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="114" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="115" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="116" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="117" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="118" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="119" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="120" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="121" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="122" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="123" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="124" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="125" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="126" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="127" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="128" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="129" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="130" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="131" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="132" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="133" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="134" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="135" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="136" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="137" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="138" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="139" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="140" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="141" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="142" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="143" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="144" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="145" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="146" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="147" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="148" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="149" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="150" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="151" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="152" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="153" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="154" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="155" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="156" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="157" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="158" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="159" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="160" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="161" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="162" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="163" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="164" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="165" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="166" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="167" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="168" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="169" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="170" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="171" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="172" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="173" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="174" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="175" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="176" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="I6:I10"/>
+    <mergeCell ref="I12:I16"/>
+    <mergeCell ref="K6:O10"/>
+    <mergeCell ref="K12:O16"/>
+    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="M34:O34"/>
+    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A50:K50"/>
     <mergeCell ref="M36:M38"/>
     <mergeCell ref="M40:M42"/>
@@ -2836,19 +2846,6 @@
     <mergeCell ref="O36:O38"/>
     <mergeCell ref="O40:O42"/>
     <mergeCell ref="O44:O46"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="M18:O18"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="M34:O34"/>
-    <mergeCell ref="I6:I10"/>
-    <mergeCell ref="I12:I16"/>
-    <mergeCell ref="K6:O10"/>
-    <mergeCell ref="K12:O16"/>
-    <mergeCell ref="A4:O4"/>
-    <mergeCell ref="A18:C18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2920,7 +2917,7 @@
       <c r="A3" s="23"/>
     </row>
     <row r="4" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="82" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="10"/>
@@ -2947,11 +2944,11 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="34"/>
+      <c r="A5" s="82"/>
       <c r="B5" s="10"/>
     </row>
     <row r="6" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A6" s="34"/>
+      <c r="A6" s="82"/>
       <c r="B6" s="10"/>
       <c r="C6" s="4" t="s">
         <v>27</v>
@@ -2994,7 +2991,7 @@
       <c r="B8" s="10"/>
     </row>
     <row r="9" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="82" t="s">
         <v>54</v>
       </c>
       <c r="B9" s="10"/>
@@ -3021,11 +3018,11 @@
       </c>
     </row>
     <row r="10" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="34"/>
+      <c r="A10" s="82"/>
       <c r="B10" s="10"/>
     </row>
     <row r="11" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A11" s="34"/>
+      <c r="A11" s="82"/>
       <c r="B11" s="10"/>
       <c r="C11" s="7" t="s">
         <v>75</v>
@@ -3053,7 +3050,7 @@
       <c r="B13" s="11"/>
     </row>
     <row r="14" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="82" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="10"/>
@@ -3080,11 +3077,11 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="34"/>
+      <c r="A15" s="82"/>
       <c r="B15" s="10"/>
     </row>
     <row r="16" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A16" s="34"/>
+      <c r="A16" s="82"/>
       <c r="B16" s="10"/>
       <c r="C16" s="4" t="s">
         <v>26</v>
@@ -3109,11 +3106,11 @@
       </c>
     </row>
     <row r="17" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="34"/>
+      <c r="A17" s="82"/>
       <c r="B17" s="10"/>
     </row>
     <row r="18" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A18" s="34"/>
+      <c r="A18" s="82"/>
       <c r="B18" s="10"/>
       <c r="C18" s="5" t="s">
         <v>68</v>
@@ -3197,7 +3194,7 @@
       <c r="B23" s="11"/>
     </row>
     <row r="24" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A24" s="34" t="s">
+      <c r="A24" s="82" t="s">
         <v>32</v>
       </c>
       <c r="B24" s="10"/>
@@ -3224,11 +3221,11 @@
       </c>
     </row>
     <row r="25" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="34"/>
+      <c r="A25" s="82"/>
       <c r="B25" s="10"/>
     </row>
     <row r="26" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A26" s="34"/>
+      <c r="A26" s="82"/>
       <c r="B26" s="10"/>
       <c r="C26" s="5" t="s">
         <v>38</v>
@@ -3241,6 +3238,9 @@
       </c>
       <c r="I26" s="12" t="s">
         <v>73</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3265,7 +3265,7 @@
       <c r="B28" s="11"/>
     </row>
     <row r="29" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A29" s="34" t="s">
+      <c r="A29" s="82" t="s">
         <v>40</v>
       </c>
       <c r="B29" s="10"/>
@@ -3292,11 +3292,11 @@
       </c>
     </row>
     <row r="30" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="34"/>
+      <c r="A30" s="82"/>
       <c r="B30" s="10"/>
     </row>
     <row r="31" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A31" s="34"/>
+      <c r="A31" s="82"/>
       <c r="B31" s="10"/>
       <c r="C31" s="7" t="s">
         <v>45</v>
@@ -3327,7 +3327,7 @@
       <c r="B33" s="11"/>
     </row>
     <row r="34" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A34" s="34" t="s">
+      <c r="A34" s="82" t="s">
         <v>47</v>
       </c>
       <c r="B34" s="10"/>
@@ -3354,11 +3354,11 @@
       </c>
     </row>
     <row r="35" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="34"/>
+      <c r="A35" s="82"/>
       <c r="B35" s="10"/>
     </row>
     <row r="36" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A36" s="34"/>
+      <c r="A36" s="82"/>
       <c r="B36" s="10"/>
       <c r="C36" s="5" t="s">
         <v>7</v>

--- a/images/2024-07-01-Omnissa-poc/Omnissa-adoption-map.xlsx
+++ b/images/2024-07-01-Omnissa-poc/Omnissa-adoption-map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mbeaugrand/github/blog/images/2024-07-01-Omnissa-poc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EDDFFF8-6D40-3F46-9589-B820A7ECD273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEFEBA9C-F9D3-3841-B11B-6B4BD589FB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15680" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14480" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Company profile" sheetId="3" r:id="rId1"/>
@@ -531,7 +531,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -611,20 +611,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="18"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
+      <sz val="12"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -672,26 +666,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF0070C0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="4"/>
       </patternFill>
     </fill>
   </fills>
@@ -891,13 +866,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -979,68 +955,77 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1051,80 +1036,60 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
+    <cellStyle name="Accent1" xfId="4" builtinId="29"/>
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Neutral" xfId="3" builtinId="28"/>
@@ -1583,7 +1548,7 @@
       <c r="N2" s="21"/>
       <c r="O2" s="22"/>
     </row>
-    <row r="3" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="34"/>
       <c r="B3" s="34"/>
       <c r="C3" s="34"/>
@@ -1600,26 +1565,26 @@
       <c r="N3" s="34"/>
       <c r="O3" s="34"/>
     </row>
-    <row r="4" spans="1:15" s="36" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="81" t="s">
+    <row r="4" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="B4" s="81"/>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="81"/>
-      <c r="K4" s="81"/>
-      <c r="L4" s="81"/>
-      <c r="M4" s="81"/>
-      <c r="N4" s="81"/>
-      <c r="O4" s="81"/>
-    </row>
-    <row r="5" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="63"/>
+      <c r="L4" s="63"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="63"/>
+    </row>
+    <row r="5" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="34"/>
       <c r="B5" s="34"/>
       <c r="C5" s="34"/>
@@ -1636,30 +1601,30 @@
       <c r="N5" s="34"/>
       <c r="O5" s="34"/>
     </row>
-    <row r="6" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="35" t="s">
+    <row r="6" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="64" t="s">
         <v>77</v>
       </c>
       <c r="B6" s="34"/>
-      <c r="C6" s="37"/>
+      <c r="C6" s="36"/>
       <c r="D6" s="34"/>
-      <c r="E6" s="38" t="s">
+      <c r="E6" s="65" t="s">
         <v>84</v>
       </c>
       <c r="F6" s="34"/>
-      <c r="G6" s="39"/>
+      <c r="G6" s="37"/>
       <c r="H6" s="34"/>
-      <c r="I6" s="61" t="s">
+      <c r="I6" s="66" t="s">
         <v>90</v>
       </c>
       <c r="J6" s="34"/>
-      <c r="K6" s="63"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="65"/>
-    </row>
-    <row r="7" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K6" s="41"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="43"/>
+    </row>
+    <row r="7" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="34"/>
       <c r="B7" s="34"/>
       <c r="C7" s="34"/>
@@ -1668,36 +1633,36 @@
       <c r="F7" s="34"/>
       <c r="G7" s="34"/>
       <c r="H7" s="34"/>
-      <c r="I7" s="61"/>
+      <c r="I7" s="66"/>
       <c r="J7" s="34"/>
-      <c r="K7" s="66"/>
-      <c r="L7" s="67"/>
-      <c r="M7" s="67"/>
-      <c r="N7" s="67"/>
-      <c r="O7" s="68"/>
-    </row>
-    <row r="8" spans="1:15" s="36" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="35" t="s">
+      <c r="K7" s="44"/>
+      <c r="L7" s="45"/>
+      <c r="M7" s="45"/>
+      <c r="N7" s="45"/>
+      <c r="O7" s="46"/>
+    </row>
+    <row r="8" spans="1:15" s="35" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="64" t="s">
         <v>78</v>
       </c>
       <c r="B8" s="34"/>
-      <c r="C8" s="40"/>
+      <c r="C8" s="38"/>
       <c r="D8" s="34"/>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="64" t="s">
         <v>85</v>
       </c>
       <c r="F8" s="34"/>
-      <c r="G8" s="40"/>
+      <c r="G8" s="38"/>
       <c r="H8" s="34"/>
-      <c r="I8" s="61"/>
+      <c r="I8" s="66"/>
       <c r="J8" s="34"/>
-      <c r="K8" s="66"/>
-      <c r="L8" s="67"/>
-      <c r="M8" s="67"/>
-      <c r="N8" s="67"/>
-      <c r="O8" s="68"/>
-    </row>
-    <row r="9" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K8" s="44"/>
+      <c r="L8" s="45"/>
+      <c r="M8" s="45"/>
+      <c r="N8" s="45"/>
+      <c r="O8" s="46"/>
+    </row>
+    <row r="9" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="34"/>
       <c r="B9" s="34"/>
       <c r="C9" s="34"/>
@@ -1706,36 +1671,36 @@
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
       <c r="H9" s="34"/>
-      <c r="I9" s="61"/>
+      <c r="I9" s="66"/>
       <c r="J9" s="34"/>
-      <c r="K9" s="66"/>
-      <c r="L9" s="67"/>
-      <c r="M9" s="67"/>
-      <c r="N9" s="67"/>
-      <c r="O9" s="68"/>
-    </row>
-    <row r="10" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="35" t="s">
+      <c r="K9" s="44"/>
+      <c r="L9" s="45"/>
+      <c r="M9" s="45"/>
+      <c r="N9" s="45"/>
+      <c r="O9" s="46"/>
+    </row>
+    <row r="10" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="64" t="s">
         <v>79</v>
       </c>
       <c r="B10" s="34"/>
-      <c r="C10" s="40"/>
+      <c r="C10" s="38"/>
       <c r="D10" s="34"/>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="64" t="s">
         <v>86</v>
       </c>
       <c r="F10" s="34"/>
-      <c r="G10" s="40"/>
+      <c r="G10" s="38"/>
       <c r="H10" s="34"/>
-      <c r="I10" s="61"/>
+      <c r="I10" s="66"/>
       <c r="J10" s="34"/>
-      <c r="K10" s="69"/>
-      <c r="L10" s="70"/>
-      <c r="M10" s="70"/>
-      <c r="N10" s="70"/>
-      <c r="O10" s="71"/>
-    </row>
-    <row r="11" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K10" s="47"/>
+      <c r="L10" s="48"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="49"/>
+    </row>
+    <row r="11" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="34"/>
       <c r="B11" s="34"/>
       <c r="C11" s="34"/>
@@ -1752,30 +1717,30 @@
       <c r="N11" s="34"/>
       <c r="O11" s="34"/>
     </row>
-    <row r="12" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="35" t="s">
+    <row r="12" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="64" t="s">
         <v>81</v>
       </c>
       <c r="B12" s="34"/>
-      <c r="C12" s="40"/>
+      <c r="C12" s="38"/>
       <c r="D12" s="34"/>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="64" t="s">
         <v>87</v>
       </c>
       <c r="F12" s="34"/>
-      <c r="G12" s="40"/>
+      <c r="G12" s="38"/>
       <c r="H12" s="34"/>
-      <c r="I12" s="62" t="s">
+      <c r="I12" s="67" t="s">
         <v>91</v>
       </c>
       <c r="J12" s="34"/>
-      <c r="K12" s="72"/>
-      <c r="L12" s="73"/>
-      <c r="M12" s="73"/>
-      <c r="N12" s="73"/>
-      <c r="O12" s="74"/>
-    </row>
-    <row r="13" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K12" s="50"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="51"/>
+      <c r="N12" s="51"/>
+      <c r="O12" s="52"/>
+    </row>
+    <row r="13" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="34"/>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -1784,36 +1749,36 @@
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="34"/>
-      <c r="I13" s="62"/>
+      <c r="I13" s="67"/>
       <c r="J13" s="34"/>
-      <c r="K13" s="75"/>
-      <c r="L13" s="76"/>
-      <c r="M13" s="76"/>
-      <c r="N13" s="76"/>
-      <c r="O13" s="77"/>
-    </row>
-    <row r="14" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="35" t="s">
+      <c r="K13" s="53"/>
+      <c r="L13" s="54"/>
+      <c r="M13" s="54"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="55"/>
+    </row>
+    <row r="14" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="64" t="s">
         <v>82</v>
       </c>
       <c r="B14" s="34"/>
-      <c r="C14" s="37"/>
+      <c r="C14" s="36"/>
       <c r="D14" s="34"/>
-      <c r="E14" s="38" t="s">
+      <c r="E14" s="65" t="s">
         <v>88</v>
       </c>
       <c r="F14" s="34"/>
-      <c r="G14" s="39"/>
+      <c r="G14" s="37"/>
       <c r="H14" s="34"/>
-      <c r="I14" s="62"/>
+      <c r="I14" s="67"/>
       <c r="J14" s="34"/>
-      <c r="K14" s="75"/>
-      <c r="L14" s="76"/>
-      <c r="M14" s="76"/>
-      <c r="N14" s="76"/>
-      <c r="O14" s="77"/>
-    </row>
-    <row r="15" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K14" s="53"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="54"/>
+      <c r="N14" s="54"/>
+      <c r="O14" s="55"/>
+    </row>
+    <row r="15" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="34"/>
       <c r="B15" s="34"/>
       <c r="C15" s="34"/>
@@ -1822,36 +1787,36 @@
       <c r="F15" s="34"/>
       <c r="G15" s="34"/>
       <c r="H15" s="34"/>
-      <c r="I15" s="62"/>
+      <c r="I15" s="67"/>
       <c r="J15" s="34"/>
-      <c r="K15" s="75"/>
-      <c r="L15" s="76"/>
-      <c r="M15" s="76"/>
-      <c r="N15" s="76"/>
-      <c r="O15" s="77"/>
-    </row>
-    <row r="16" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="35" t="s">
+      <c r="K15" s="53"/>
+      <c r="L15" s="54"/>
+      <c r="M15" s="54"/>
+      <c r="N15" s="54"/>
+      <c r="O15" s="55"/>
+    </row>
+    <row r="16" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="64" t="s">
         <v>83</v>
       </c>
       <c r="B16" s="34"/>
-      <c r="C16" s="37"/>
+      <c r="C16" s="36"/>
       <c r="D16" s="34"/>
-      <c r="E16" s="41" t="s">
+      <c r="E16" s="65" t="s">
         <v>89</v>
       </c>
       <c r="F16" s="34"/>
-      <c r="G16" s="37"/>
+      <c r="G16" s="36"/>
       <c r="H16" s="34"/>
-      <c r="I16" s="62"/>
+      <c r="I16" s="67"/>
       <c r="J16" s="34"/>
-      <c r="K16" s="78"/>
-      <c r="L16" s="79"/>
-      <c r="M16" s="79"/>
-      <c r="N16" s="79"/>
-      <c r="O16" s="80"/>
-    </row>
-    <row r="17" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K16" s="56"/>
+      <c r="L16" s="57"/>
+      <c r="M16" s="57"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="58"/>
+    </row>
+    <row r="17" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="34"/>
       <c r="B17" s="34"/>
       <c r="C17" s="34"/>
@@ -1868,32 +1833,32 @@
       <c r="N17" s="34"/>
       <c r="O17" s="34"/>
     </row>
-    <row r="18" spans="1:15" s="36" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="59" t="s">
+    <row r="18" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="B18" s="59"/>
-      <c r="C18" s="59"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="68"/>
       <c r="D18" s="34"/>
-      <c r="E18" s="59" t="s">
+      <c r="E18" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="F18" s="59"/>
-      <c r="G18" s="59"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="68"/>
       <c r="H18" s="34"/>
-      <c r="I18" s="59" t="s">
+      <c r="I18" s="68" t="s">
         <v>108</v>
       </c>
-      <c r="J18" s="59"/>
-      <c r="K18" s="59"/>
+      <c r="J18" s="68"/>
+      <c r="K18" s="68"/>
       <c r="L18" s="34"/>
-      <c r="M18" s="59" t="s">
+      <c r="M18" s="68" t="s">
         <v>116</v>
       </c>
-      <c r="N18" s="59"/>
-      <c r="O18" s="59"/>
-    </row>
-    <row r="19" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N18" s="68"/>
+      <c r="O18" s="68"/>
+    </row>
+    <row r="19" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="34"/>
       <c r="B19" s="34"/>
       <c r="C19" s="34"/>
@@ -1910,32 +1875,32 @@
       <c r="N19" s="34"/>
       <c r="O19" s="34"/>
     </row>
-    <row r="20" spans="1:15" s="36" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="42" t="s">
+    <row r="20" spans="1:15" s="35" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="69" t="s">
         <v>93</v>
       </c>
       <c r="B20" s="34"/>
-      <c r="C20" s="40"/>
+      <c r="C20" s="38"/>
       <c r="D20" s="34"/>
-      <c r="E20" s="42" t="s">
+      <c r="E20" s="69" t="s">
         <v>101</v>
       </c>
       <c r="F20" s="34"/>
-      <c r="G20" s="40"/>
+      <c r="G20" s="38"/>
       <c r="H20" s="34"/>
-      <c r="I20" s="42" t="s">
+      <c r="I20" s="69" t="s">
         <v>109</v>
       </c>
       <c r="J20" s="34"/>
-      <c r="K20" s="40"/>
+      <c r="K20" s="38"/>
       <c r="L20" s="34"/>
-      <c r="M20" s="42" t="s">
+      <c r="M20" s="69" t="s">
         <v>117</v>
       </c>
       <c r="N20" s="34"/>
-      <c r="O20" s="40"/>
-    </row>
-    <row r="21" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O20" s="38"/>
+    </row>
+    <row r="21" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="34"/>
       <c r="B21" s="34"/>
       <c r="C21" s="34"/>
@@ -1952,32 +1917,32 @@
       <c r="N21" s="34"/>
       <c r="O21" s="34"/>
     </row>
-    <row r="22" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="42" t="s">
+    <row r="22" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="69" t="s">
         <v>94</v>
       </c>
       <c r="B22" s="34"/>
-      <c r="C22" s="40"/>
+      <c r="C22" s="38"/>
       <c r="D22" s="34"/>
-      <c r="E22" s="42" t="s">
+      <c r="E22" s="69" t="s">
         <v>102</v>
       </c>
       <c r="F22" s="34"/>
-      <c r="G22" s="40"/>
+      <c r="G22" s="38"/>
       <c r="H22" s="34"/>
-      <c r="I22" s="42" t="s">
+      <c r="I22" s="69" t="s">
         <v>110</v>
       </c>
       <c r="J22" s="34"/>
-      <c r="K22" s="40"/>
+      <c r="K22" s="38"/>
       <c r="L22" s="34"/>
-      <c r="M22" s="42" t="s">
+      <c r="M22" s="69" t="s">
         <v>118</v>
       </c>
       <c r="N22" s="34"/>
-      <c r="O22" s="40"/>
-    </row>
-    <row r="23" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O22" s="38"/>
+    </row>
+    <row r="23" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="34"/>
       <c r="B23" s="34"/>
       <c r="C23" s="34"/>
@@ -1994,32 +1959,32 @@
       <c r="N23" s="34"/>
       <c r="O23" s="34"/>
     </row>
-    <row r="24" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="42" t="s">
+    <row r="24" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="69" t="s">
         <v>95</v>
       </c>
       <c r="B24" s="34"/>
-      <c r="C24" s="37"/>
+      <c r="C24" s="36"/>
       <c r="D24" s="34"/>
-      <c r="E24" s="43" t="s">
+      <c r="E24" s="70" t="s">
         <v>103</v>
       </c>
       <c r="F24" s="34"/>
-      <c r="G24" s="39"/>
+      <c r="G24" s="37"/>
       <c r="H24" s="34"/>
-      <c r="I24" s="43" t="s">
+      <c r="I24" s="70" t="s">
         <v>111</v>
       </c>
       <c r="J24" s="34"/>
-      <c r="K24" s="37"/>
+      <c r="K24" s="36"/>
       <c r="L24" s="34"/>
-      <c r="M24" s="44" t="s">
+      <c r="M24" s="70" t="s">
         <v>119</v>
       </c>
       <c r="N24" s="34"/>
-      <c r="O24" s="37"/>
-    </row>
-    <row r="25" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O24" s="36"/>
+    </row>
+    <row r="25" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="34"/>
       <c r="B25" s="34"/>
       <c r="C25" s="34"/>
@@ -2036,32 +2001,32 @@
       <c r="N25" s="34"/>
       <c r="O25" s="34"/>
     </row>
-    <row r="26" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="42" t="s">
+    <row r="26" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="69" t="s">
         <v>96</v>
       </c>
       <c r="B26" s="34"/>
-      <c r="C26" s="39"/>
+      <c r="C26" s="37"/>
       <c r="D26" s="34"/>
-      <c r="E26" s="43" t="s">
+      <c r="E26" s="70" t="s">
         <v>104</v>
       </c>
       <c r="F26" s="34"/>
-      <c r="G26" s="40"/>
+      <c r="G26" s="38"/>
       <c r="H26" s="34"/>
-      <c r="I26" s="42" t="s">
+      <c r="I26" s="69" t="s">
         <v>112</v>
       </c>
       <c r="J26" s="34"/>
-      <c r="K26" s="40"/>
+      <c r="K26" s="38"/>
       <c r="L26" s="34"/>
-      <c r="M26" s="42" t="s">
+      <c r="M26" s="69" t="s">
         <v>120</v>
       </c>
       <c r="N26" s="34"/>
-      <c r="O26" s="40"/>
-    </row>
-    <row r="27" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O26" s="38"/>
+    </row>
+    <row r="27" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="34"/>
       <c r="B27" s="34"/>
       <c r="C27" s="34"/>
@@ -2078,32 +2043,32 @@
       <c r="N27" s="34"/>
       <c r="O27" s="34"/>
     </row>
-    <row r="28" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="42" t="s">
+    <row r="28" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="69" t="s">
         <v>97</v>
       </c>
       <c r="B28" s="34"/>
-      <c r="C28" s="40"/>
+      <c r="C28" s="38"/>
       <c r="D28" s="34"/>
-      <c r="E28" s="42" t="s">
+      <c r="E28" s="69" t="s">
         <v>105</v>
       </c>
       <c r="F28" s="34"/>
-      <c r="G28" s="40"/>
+      <c r="G28" s="38"/>
       <c r="H28" s="34"/>
-      <c r="I28" s="42" t="s">
+      <c r="I28" s="69" t="s">
         <v>113</v>
       </c>
       <c r="J28" s="34"/>
-      <c r="K28" s="40"/>
+      <c r="K28" s="38"/>
       <c r="L28" s="34"/>
-      <c r="M28" s="42" t="s">
+      <c r="M28" s="69" t="s">
         <v>121</v>
       </c>
       <c r="N28" s="34"/>
-      <c r="O28" s="40"/>
-    </row>
-    <row r="29" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O28" s="38"/>
+    </row>
+    <row r="29" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="34"/>
       <c r="B29" s="34"/>
       <c r="C29" s="34"/>
@@ -2120,32 +2085,32 @@
       <c r="N29" s="34"/>
       <c r="O29" s="34"/>
     </row>
-    <row r="30" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="42" t="s">
+    <row r="30" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="69" t="s">
         <v>98</v>
       </c>
       <c r="B30" s="34"/>
-      <c r="C30" s="40"/>
+      <c r="C30" s="38"/>
       <c r="D30" s="34"/>
-      <c r="E30" s="42" t="s">
+      <c r="E30" s="69" t="s">
         <v>106</v>
       </c>
       <c r="F30" s="34"/>
-      <c r="G30" s="40"/>
+      <c r="G30" s="38"/>
       <c r="H30" s="34"/>
-      <c r="I30" s="42" t="s">
+      <c r="I30" s="69" t="s">
         <v>114</v>
       </c>
       <c r="J30" s="34"/>
-      <c r="K30" s="40"/>
+      <c r="K30" s="38"/>
       <c r="L30" s="34"/>
-      <c r="M30" s="42" t="s">
+      <c r="M30" s="69" t="s">
         <v>122</v>
       </c>
       <c r="N30" s="34"/>
-      <c r="O30" s="40"/>
-    </row>
-    <row r="31" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O30" s="38"/>
+    </row>
+    <row r="31" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="34"/>
       <c r="B31" s="34"/>
       <c r="C31" s="34"/>
@@ -2162,32 +2127,32 @@
       <c r="N31" s="34"/>
       <c r="O31" s="34"/>
     </row>
-    <row r="32" spans="1:15" s="36" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="42" t="s">
+    <row r="32" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="69" t="s">
         <v>99</v>
       </c>
       <c r="B32" s="34"/>
-      <c r="C32" s="40"/>
+      <c r="C32" s="38"/>
       <c r="D32" s="34"/>
-      <c r="E32" s="42" t="s">
+      <c r="E32" s="69" t="s">
         <v>107</v>
       </c>
       <c r="F32" s="34"/>
-      <c r="G32" s="40"/>
+      <c r="G32" s="38"/>
       <c r="H32" s="34"/>
-      <c r="I32" s="42" t="s">
+      <c r="I32" s="69" t="s">
         <v>115</v>
       </c>
       <c r="J32" s="34"/>
-      <c r="K32" s="40"/>
+      <c r="K32" s="38"/>
       <c r="L32" s="34"/>
-      <c r="M32" s="42" t="s">
+      <c r="M32" s="69" t="s">
         <v>123</v>
       </c>
       <c r="N32" s="34"/>
-      <c r="O32" s="40"/>
-    </row>
-    <row r="33" spans="1:15" s="36" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O32" s="38"/>
+    </row>
+    <row r="33" spans="1:15" s="35" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="34"/>
       <c r="B33" s="34"/>
       <c r="C33" s="34"/>
@@ -2204,32 +2169,32 @@
       <c r="N33" s="34"/>
       <c r="O33" s="34"/>
     </row>
-    <row r="34" spans="1:15" s="36" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="60" t="s">
+    <row r="34" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="71" t="s">
         <v>124</v>
       </c>
-      <c r="B34" s="60"/>
-      <c r="C34" s="60"/>
+      <c r="B34" s="71"/>
+      <c r="C34" s="71"/>
       <c r="D34" s="34"/>
-      <c r="E34" s="60" t="s">
+      <c r="E34" s="71" t="s">
         <v>125</v>
       </c>
-      <c r="F34" s="60"/>
-      <c r="G34" s="60"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
       <c r="H34" s="34"/>
-      <c r="I34" s="60" t="s">
+      <c r="I34" s="71" t="s">
         <v>126</v>
       </c>
-      <c r="J34" s="60"/>
-      <c r="K34" s="60"/>
+      <c r="J34" s="71"/>
+      <c r="K34" s="71"/>
       <c r="L34" s="34"/>
-      <c r="M34" s="60" t="s">
+      <c r="M34" s="71" t="s">
         <v>127</v>
       </c>
-      <c r="N34" s="60"/>
-      <c r="O34" s="60"/>
-    </row>
-    <row r="35" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N34" s="71"/>
+      <c r="O34" s="71"/>
+    </row>
+    <row r="35" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="34"/>
       <c r="B35" s="34"/>
       <c r="C35" s="34"/>
@@ -2246,32 +2211,32 @@
       <c r="N35" s="34"/>
       <c r="O35" s="34"/>
     </row>
-    <row r="36" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="46" t="s">
+    <row r="36" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="72" t="s">
         <v>22</v>
       </c>
       <c r="B36" s="34"/>
-      <c r="C36" s="39"/>
+      <c r="C36" s="37"/>
       <c r="D36" s="34"/>
-      <c r="E36" s="45" t="s">
+      <c r="E36" s="73" t="s">
         <v>132</v>
       </c>
       <c r="F36" s="34"/>
-      <c r="G36" s="39"/>
+      <c r="G36" s="37"/>
       <c r="H36" s="34"/>
-      <c r="I36" s="45" t="s">
+      <c r="I36" s="73" t="s">
         <v>138</v>
       </c>
       <c r="J36" s="34"/>
-      <c r="K36" s="39"/>
+      <c r="K36" s="37"/>
       <c r="L36" s="34"/>
-      <c r="M36" s="54" t="s">
+      <c r="M36" s="75" t="s">
         <v>145</v>
       </c>
       <c r="N36" s="34"/>
-      <c r="O36" s="56"/>
-    </row>
-    <row r="37" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O36" s="59"/>
+    </row>
+    <row r="37" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="34"/>
       <c r="B37" s="34"/>
       <c r="C37" s="34"/>
@@ -2284,34 +2249,34 @@
       <c r="J37" s="34"/>
       <c r="K37" s="34"/>
       <c r="L37" s="34"/>
-      <c r="M37" s="54"/>
+      <c r="M37" s="75"/>
       <c r="N37" s="34"/>
-      <c r="O37" s="57"/>
-    </row>
-    <row r="38" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="46" t="s">
+      <c r="O37" s="60"/>
+    </row>
+    <row r="38" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="72" t="s">
         <v>23</v>
       </c>
       <c r="B38" s="34"/>
-      <c r="C38" s="40"/>
+      <c r="C38" s="38"/>
       <c r="D38" s="34"/>
-      <c r="E38" s="46" t="s">
+      <c r="E38" s="72" t="s">
         <v>133</v>
       </c>
       <c r="F38" s="34"/>
-      <c r="G38" s="40"/>
+      <c r="G38" s="38"/>
       <c r="H38" s="34"/>
-      <c r="I38" s="46" t="s">
+      <c r="I38" s="72" t="s">
         <v>139</v>
       </c>
       <c r="J38" s="34"/>
-      <c r="K38" s="40"/>
+      <c r="K38" s="38"/>
       <c r="L38" s="34"/>
-      <c r="M38" s="54"/>
+      <c r="M38" s="75"/>
       <c r="N38" s="34"/>
-      <c r="O38" s="58"/>
-    </row>
-    <row r="39" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O38" s="61"/>
+    </row>
+    <row r="39" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="34"/>
       <c r="B39" s="34"/>
       <c r="C39" s="34"/>
@@ -2328,32 +2293,32 @@
       <c r="N39" s="34"/>
       <c r="O39" s="34"/>
     </row>
-    <row r="40" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="46" t="s">
+    <row r="40" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="72" t="s">
         <v>128</v>
       </c>
       <c r="B40" s="34"/>
-      <c r="C40" s="40"/>
+      <c r="C40" s="38"/>
       <c r="D40" s="34"/>
-      <c r="E40" s="46" t="s">
+      <c r="E40" s="72" t="s">
         <v>134</v>
       </c>
       <c r="F40" s="34"/>
-      <c r="G40" s="40"/>
+      <c r="G40" s="38"/>
       <c r="H40" s="34"/>
-      <c r="I40" s="47" t="s">
+      <c r="I40" s="73" t="s">
         <v>140</v>
       </c>
       <c r="J40" s="34"/>
-      <c r="K40" s="48"/>
+      <c r="K40" s="39"/>
       <c r="L40" s="34"/>
-      <c r="M40" s="54" t="s">
+      <c r="M40" s="75" t="s">
         <v>146</v>
       </c>
       <c r="N40" s="34"/>
-      <c r="O40" s="56"/>
-    </row>
-    <row r="41" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O40" s="59"/>
+    </row>
+    <row r="41" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="34"/>
       <c r="B41" s="34"/>
       <c r="C41" s="34"/>
@@ -2366,34 +2331,34 @@
       <c r="J41" s="34"/>
       <c r="K41" s="34"/>
       <c r="L41" s="34"/>
-      <c r="M41" s="54"/>
+      <c r="M41" s="75"/>
       <c r="N41" s="34"/>
-      <c r="O41" s="57"/>
-    </row>
-    <row r="42" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="46" t="s">
+      <c r="O41" s="60"/>
+    </row>
+    <row r="42" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="72" t="s">
         <v>129</v>
       </c>
       <c r="B42" s="34"/>
-      <c r="C42" s="40"/>
+      <c r="C42" s="38"/>
       <c r="D42" s="34"/>
-      <c r="E42" s="46" t="s">
+      <c r="E42" s="72" t="s">
         <v>135</v>
       </c>
       <c r="F42" s="34"/>
-      <c r="G42" s="40"/>
+      <c r="G42" s="38"/>
       <c r="H42" s="34"/>
-      <c r="I42" s="46" t="s">
+      <c r="I42" s="72" t="s">
         <v>141</v>
       </c>
       <c r="J42" s="34"/>
-      <c r="K42" s="40"/>
+      <c r="K42" s="38"/>
       <c r="L42" s="34"/>
-      <c r="M42" s="54"/>
+      <c r="M42" s="75"/>
       <c r="N42" s="34"/>
-      <c r="O42" s="58"/>
-    </row>
-    <row r="43" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O42" s="61"/>
+    </row>
+    <row r="43" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="34"/>
       <c r="B43" s="34"/>
       <c r="C43" s="34"/>
@@ -2410,32 +2375,32 @@
       <c r="N43" s="34"/>
       <c r="O43" s="34"/>
     </row>
-    <row r="44" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="46" t="s">
+    <row r="44" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="72" t="s">
         <v>130</v>
       </c>
       <c r="B44" s="34"/>
-      <c r="C44" s="40"/>
+      <c r="C44" s="38"/>
       <c r="D44" s="34"/>
-      <c r="E44" s="46" t="s">
+      <c r="E44" s="72" t="s">
         <v>136</v>
       </c>
       <c r="F44" s="34"/>
-      <c r="G44" s="40"/>
+      <c r="G44" s="38"/>
       <c r="H44" s="34"/>
-      <c r="I44" s="46" t="s">
+      <c r="I44" s="72" t="s">
         <v>142</v>
       </c>
       <c r="J44" s="34"/>
-      <c r="K44" s="40"/>
+      <c r="K44" s="38"/>
       <c r="L44" s="34"/>
-      <c r="M44" s="55" t="s">
+      <c r="M44" s="74" t="s">
         <v>147</v>
       </c>
       <c r="N44" s="34"/>
-      <c r="O44" s="56"/>
-    </row>
-    <row r="45" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O44" s="59"/>
+    </row>
+    <row r="45" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="34"/>
       <c r="B45" s="34"/>
       <c r="C45" s="34"/>
@@ -2448,34 +2413,34 @@
       <c r="J45" s="34"/>
       <c r="K45" s="34"/>
       <c r="L45" s="34"/>
-      <c r="M45" s="55"/>
+      <c r="M45" s="74"/>
       <c r="N45" s="34"/>
-      <c r="O45" s="57"/>
-    </row>
-    <row r="46" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="46" t="s">
+      <c r="O45" s="60"/>
+    </row>
+    <row r="46" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="72" t="s">
         <v>131</v>
       </c>
       <c r="B46" s="34"/>
-      <c r="C46" s="40"/>
+      <c r="C46" s="38"/>
       <c r="D46" s="34"/>
-      <c r="E46" s="46" t="s">
+      <c r="E46" s="72" t="s">
         <v>137</v>
       </c>
       <c r="F46" s="34"/>
-      <c r="G46" s="40"/>
+      <c r="G46" s="38"/>
       <c r="H46" s="34"/>
-      <c r="I46" s="46" t="s">
+      <c r="I46" s="72" t="s">
         <v>143</v>
       </c>
       <c r="J46" s="34"/>
-      <c r="K46" s="40"/>
+      <c r="K46" s="38"/>
       <c r="L46" s="34"/>
-      <c r="M46" s="55"/>
+      <c r="M46" s="74"/>
       <c r="N46" s="34"/>
-      <c r="O46" s="58"/>
-    </row>
-    <row r="47" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O46" s="61"/>
+    </row>
+    <row r="47" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="34"/>
       <c r="B47" s="34"/>
       <c r="C47" s="34"/>
@@ -2492,29 +2457,29 @@
       <c r="N47" s="34"/>
       <c r="O47" s="34"/>
     </row>
-    <row r="48" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I48" s="46" t="s">
+    <row r="48" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I48" s="72" t="s">
         <v>144</v>
       </c>
-      <c r="K48" s="49"/>
-    </row>
-    <row r="49" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" spans="1:15" s="36" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="53" t="s">
+      <c r="K48" s="40"/>
+    </row>
+    <row r="49" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="B50" s="53"/>
-      <c r="C50" s="53"/>
-      <c r="D50" s="53"/>
-      <c r="E50" s="53"/>
-      <c r="F50" s="53"/>
-      <c r="G50" s="53"/>
-      <c r="H50" s="53"/>
-      <c r="I50" s="53"/>
-      <c r="J50" s="53"/>
-      <c r="K50" s="53"/>
-    </row>
-    <row r="51" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B50" s="76"/>
+      <c r="C50" s="76"/>
+      <c r="D50" s="76"/>
+      <c r="E50" s="76"/>
+      <c r="F50" s="76"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="76"/>
+      <c r="I50" s="76"/>
+      <c r="J50" s="76"/>
+      <c r="K50" s="76"/>
+    </row>
+    <row r="51" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="34"/>
       <c r="B51" s="34"/>
       <c r="C51" s="34"/>
@@ -2531,26 +2496,26 @@
       <c r="N51" s="34"/>
       <c r="O51" s="34"/>
     </row>
-    <row r="52" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="50" t="s">
+    <row r="52" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="77" t="s">
         <v>149</v>
       </c>
       <c r="B52" s="34"/>
-      <c r="C52" s="37"/>
+      <c r="C52" s="36"/>
       <c r="D52" s="34"/>
-      <c r="E52" s="51" t="s">
+      <c r="E52" s="78" t="s">
         <v>155</v>
       </c>
       <c r="F52" s="34"/>
-      <c r="G52" s="39"/>
+      <c r="G52" s="37"/>
       <c r="H52" s="34"/>
-      <c r="I52" s="51" t="s">
+      <c r="I52" s="78" t="s">
         <v>161</v>
       </c>
       <c r="J52" s="34"/>
-      <c r="K52" s="39"/>
-    </row>
-    <row r="53" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K52" s="37"/>
+    </row>
+    <row r="53" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="34"/>
       <c r="B53" s="34"/>
       <c r="C53" s="34"/>
@@ -2563,26 +2528,26 @@
       <c r="J53" s="34"/>
       <c r="K53" s="34"/>
     </row>
-    <row r="54" spans="1:15" s="36" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="50" t="s">
+    <row r="54" spans="1:15" s="35" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="77" t="s">
         <v>150</v>
       </c>
       <c r="B54" s="34"/>
-      <c r="C54" s="40"/>
+      <c r="C54" s="38"/>
       <c r="D54" s="34"/>
-      <c r="E54" s="50" t="s">
+      <c r="E54" s="77" t="s">
         <v>156</v>
       </c>
       <c r="F54" s="34"/>
-      <c r="G54" s="40"/>
+      <c r="G54" s="38"/>
       <c r="H54" s="34"/>
-      <c r="I54" s="50" t="s">
+      <c r="I54" s="77" t="s">
         <v>162</v>
       </c>
       <c r="J54" s="34"/>
-      <c r="K54" s="40"/>
-    </row>
-    <row r="55" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K54" s="38"/>
+    </row>
+    <row r="55" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="34"/>
       <c r="B55" s="34"/>
       <c r="C55" s="34"/>
@@ -2595,26 +2560,26 @@
       <c r="J55" s="34"/>
       <c r="K55" s="34"/>
     </row>
-    <row r="56" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="50" t="s">
+    <row r="56" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="77" t="s">
         <v>151</v>
       </c>
       <c r="B56" s="34"/>
-      <c r="C56" s="40"/>
+      <c r="C56" s="38"/>
       <c r="D56" s="34"/>
-      <c r="E56" s="50" t="s">
+      <c r="E56" s="77" t="s">
         <v>157</v>
       </c>
       <c r="F56" s="34"/>
-      <c r="G56" s="40"/>
+      <c r="G56" s="38"/>
       <c r="H56" s="34"/>
-      <c r="I56" s="50" t="s">
+      <c r="I56" s="77" t="s">
         <v>163</v>
       </c>
       <c r="J56" s="34"/>
-      <c r="K56" s="40"/>
-    </row>
-    <row r="57" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K56" s="38"/>
+    </row>
+    <row r="57" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="34"/>
       <c r="B57" s="34"/>
       <c r="C57" s="34"/>
@@ -2627,26 +2592,26 @@
       <c r="J57" s="34"/>
       <c r="K57" s="34"/>
     </row>
-    <row r="58" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="50" t="s">
+    <row r="58" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="77" t="s">
         <v>152</v>
       </c>
       <c r="B58" s="34"/>
-      <c r="C58" s="40"/>
+      <c r="C58" s="38"/>
       <c r="D58" s="34"/>
-      <c r="E58" s="50" t="s">
+      <c r="E58" s="77" t="s">
         <v>158</v>
       </c>
       <c r="F58" s="34"/>
-      <c r="G58" s="40"/>
+      <c r="G58" s="38"/>
       <c r="H58" s="34"/>
-      <c r="I58" s="50" t="s">
+      <c r="I58" s="77" t="s">
         <v>164</v>
       </c>
       <c r="J58" s="34"/>
-      <c r="K58" s="40"/>
-    </row>
-    <row r="59" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K58" s="38"/>
+    </row>
+    <row r="59" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="34"/>
       <c r="B59" s="34"/>
       <c r="C59" s="34"/>
@@ -2659,26 +2624,26 @@
       <c r="J59" s="34"/>
       <c r="K59" s="34"/>
     </row>
-    <row r="60" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="50" t="s">
+    <row r="60" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="77" t="s">
         <v>153</v>
       </c>
       <c r="B60" s="34"/>
-      <c r="C60" s="37"/>
+      <c r="C60" s="36"/>
       <c r="D60" s="34"/>
-      <c r="E60" s="51" t="s">
+      <c r="E60" s="78" t="s">
         <v>159</v>
       </c>
       <c r="F60" s="34"/>
-      <c r="G60" s="39"/>
+      <c r="G60" s="37"/>
       <c r="H60" s="34"/>
-      <c r="I60" s="51" t="s">
+      <c r="I60" s="78" t="s">
         <v>165</v>
       </c>
       <c r="J60" s="34"/>
-      <c r="K60" s="39"/>
-    </row>
-    <row r="61" spans="1:15" s="36" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K60" s="37"/>
+    </row>
+    <row r="61" spans="1:15" s="35" customFormat="1" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="34"/>
       <c r="B61" s="34"/>
       <c r="C61" s="34"/>
@@ -2691,146 +2656,148 @@
       <c r="J61" s="34"/>
       <c r="K61" s="34"/>
     </row>
-    <row r="62" spans="1:15" s="36" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="50" t="s">
+    <row r="62" spans="1:15" s="35" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="77" t="s">
         <v>154</v>
       </c>
       <c r="B62" s="34"/>
-      <c r="C62" s="37"/>
+      <c r="C62" s="36"/>
       <c r="D62" s="34"/>
-      <c r="E62" s="52" t="s">
+      <c r="E62" s="78" t="s">
         <v>160</v>
       </c>
       <c r="F62" s="34"/>
-      <c r="G62" s="37"/>
+      <c r="G62" s="36"/>
       <c r="H62" s="34"/>
-      <c r="I62" s="52" t="s">
+      <c r="I62" s="78" t="s">
         <v>166</v>
       </c>
       <c r="J62" s="34"/>
-      <c r="K62" s="37"/>
-    </row>
-    <row r="63" spans="1:15" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="1:15" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="65" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="66" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="67" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="68" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="69" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="70" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="71" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="72" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="73" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="74" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="75" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="76" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="77" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="78" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="79" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="80" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="81" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="82" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="83" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="84" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="85" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="86" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="87" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="88" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="89" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="90" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="91" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="92" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="93" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="94" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="95" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="96" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="97" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="98" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="99" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="100" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="101" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="102" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="103" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="104" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="105" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="106" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="107" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="108" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="109" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="110" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="111" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="112" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="113" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="114" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="115" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="116" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="117" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="118" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="119" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="120" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="121" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="122" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="123" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="124" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="125" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="126" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="127" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="128" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="129" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="130" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="131" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="132" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="133" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="134" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="135" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="136" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="137" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="138" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="139" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="140" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="141" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="142" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="143" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="144" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="145" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="146" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="147" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="148" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="149" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="150" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="151" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="152" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="153" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="154" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="155" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="156" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="157" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="158" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="159" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="160" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="161" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="162" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="163" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="164" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="165" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="166" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="167" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="168" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="169" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="170" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="171" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="172" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="173" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="174" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="175" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="176" s="36" customFormat="1" x14ac:dyDescent="0.2"/>
+      <c r="K62" s="36"/>
+    </row>
+    <row r="63" spans="1:15" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:15" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="65" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="66" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="68" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="69" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="70" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="71" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="72" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="73" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="74" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="75" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="76" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="77" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="78" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="79" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="80" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="81" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="82" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="83" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="84" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="85" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="86" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="87" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="88" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="89" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="90" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="91" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="92" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="93" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="94" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="95" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="96" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="97" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="98" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="99" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="100" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="101" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="102" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="103" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="104" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="105" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="106" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="107" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="108" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="109" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="110" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="111" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="112" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="113" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="114" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="115" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="116" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="117" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="118" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="119" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="120" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="121" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="122" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="123" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="124" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="125" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="126" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="127" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="128" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="129" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="130" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="131" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="132" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="133" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="134" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="135" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="136" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="137" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="138" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="139" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="140" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="141" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="142" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="143" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="144" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="145" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="146" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="147" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="148" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="149" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="150" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="151" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="152" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="153" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="154" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="155" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="156" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="157" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="158" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="159" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="160" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="161" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="162" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="163" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="164" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="165" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="166" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="167" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="168" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="169" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="170" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="171" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="172" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="173" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="174" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="175" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="176" s="35" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="I6:I10"/>
-    <mergeCell ref="I12:I16"/>
-    <mergeCell ref="K6:O10"/>
-    <mergeCell ref="K12:O16"/>
-    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="A50:K50"/>
+    <mergeCell ref="M36:M38"/>
+    <mergeCell ref="M40:M42"/>
+    <mergeCell ref="M44:M46"/>
+    <mergeCell ref="O36:O38"/>
+    <mergeCell ref="O40:O42"/>
+    <mergeCell ref="O44:O46"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="I18:K18"/>
     <mergeCell ref="M18:O18"/>
@@ -2839,13 +2806,11 @@
     <mergeCell ref="I34:K34"/>
     <mergeCell ref="M34:O34"/>
     <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A50:K50"/>
-    <mergeCell ref="M36:M38"/>
-    <mergeCell ref="M40:M42"/>
-    <mergeCell ref="M44:M46"/>
-    <mergeCell ref="O36:O38"/>
-    <mergeCell ref="O40:O42"/>
-    <mergeCell ref="O44:O46"/>
+    <mergeCell ref="I6:I10"/>
+    <mergeCell ref="I12:I16"/>
+    <mergeCell ref="K6:O10"/>
+    <mergeCell ref="K12:O16"/>
+    <mergeCell ref="A4:O4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2917,7 +2882,7 @@
       <c r="A3" s="23"/>
     </row>
     <row r="4" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="62" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="10"/>
@@ -2944,11 +2909,11 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="82"/>
+      <c r="A5" s="62"/>
       <c r="B5" s="10"/>
     </row>
     <row r="6" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A6" s="82"/>
+      <c r="A6" s="62"/>
       <c r="B6" s="10"/>
       <c r="C6" s="4" t="s">
         <v>27</v>
@@ -2991,7 +2956,7 @@
       <c r="B8" s="10"/>
     </row>
     <row r="9" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A9" s="82" t="s">
+      <c r="A9" s="62" t="s">
         <v>54</v>
       </c>
       <c r="B9" s="10"/>
@@ -3018,11 +2983,11 @@
       </c>
     </row>
     <row r="10" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="82"/>
+      <c r="A10" s="62"/>
       <c r="B10" s="10"/>
     </row>
     <row r="11" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A11" s="82"/>
+      <c r="A11" s="62"/>
       <c r="B11" s="10"/>
       <c r="C11" s="7" t="s">
         <v>75</v>
@@ -3050,7 +3015,7 @@
       <c r="B13" s="11"/>
     </row>
     <row r="14" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A14" s="82" t="s">
+      <c r="A14" s="62" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="10"/>
@@ -3077,11 +3042,11 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="82"/>
+      <c r="A15" s="62"/>
       <c r="B15" s="10"/>
     </row>
     <row r="16" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A16" s="82"/>
+      <c r="A16" s="62"/>
       <c r="B16" s="10"/>
       <c r="C16" s="4" t="s">
         <v>26</v>
@@ -3106,11 +3071,11 @@
       </c>
     </row>
     <row r="17" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="82"/>
+      <c r="A17" s="62"/>
       <c r="B17" s="10"/>
     </row>
     <row r="18" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A18" s="82"/>
+      <c r="A18" s="62"/>
       <c r="B18" s="10"/>
       <c r="C18" s="5" t="s">
         <v>68</v>
@@ -3194,7 +3159,7 @@
       <c r="B23" s="11"/>
     </row>
     <row r="24" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A24" s="82" t="s">
+      <c r="A24" s="62" t="s">
         <v>32</v>
       </c>
       <c r="B24" s="10"/>
@@ -3221,11 +3186,11 @@
       </c>
     </row>
     <row r="25" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="82"/>
+      <c r="A25" s="62"/>
       <c r="B25" s="10"/>
     </row>
     <row r="26" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A26" s="82"/>
+      <c r="A26" s="62"/>
       <c r="B26" s="10"/>
       <c r="C26" s="5" t="s">
         <v>38</v>
@@ -3265,7 +3230,7 @@
       <c r="B28" s="11"/>
     </row>
     <row r="29" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A29" s="82" t="s">
+      <c r="A29" s="62" t="s">
         <v>40</v>
       </c>
       <c r="B29" s="10"/>
@@ -3292,11 +3257,11 @@
       </c>
     </row>
     <row r="30" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="82"/>
+      <c r="A30" s="62"/>
       <c r="B30" s="10"/>
     </row>
     <row r="31" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A31" s="82"/>
+      <c r="A31" s="62"/>
       <c r="B31" s="10"/>
       <c r="C31" s="7" t="s">
         <v>45</v>
@@ -3327,7 +3292,7 @@
       <c r="B33" s="11"/>
     </row>
     <row r="34" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A34" s="82" t="s">
+      <c r="A34" s="62" t="s">
         <v>47</v>
       </c>
       <c r="B34" s="10"/>
@@ -3354,11 +3319,11 @@
       </c>
     </row>
     <row r="35" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="82"/>
+      <c r="A35" s="62"/>
       <c r="B35" s="10"/>
     </row>
     <row r="36" spans="1:15" ht="19" x14ac:dyDescent="0.2">
-      <c r="A36" s="82"/>
+      <c r="A36" s="62"/>
       <c r="B36" s="10"/>
       <c r="C36" s="5" t="s">
         <v>7</v>
